--- a/research/traditional_assets/database/data/spain/spain_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_electronics_general.xlsx
@@ -587,116 +587,119 @@
           <t>Electronics (General)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.0408</v>
+      </c>
       <c r="G2">
-        <v>1.388888888888889</v>
+        <v>1.329042904290429</v>
       </c>
       <c r="H2">
-        <v>-0.4288888888888889</v>
+        <v>-0.1165016501650165</v>
       </c>
       <c r="I2">
-        <v>-0.7244444444444444</v>
+        <v>-0.1867986798679868</v>
       </c>
       <c r="J2">
-        <v>-0.7244444444444444</v>
+        <v>-0.1867986798679868</v>
       </c>
       <c r="K2">
-        <v>-1.21</v>
+        <v>-0.431</v>
       </c>
       <c r="L2">
-        <v>-0.5377777777777778</v>
+        <v>-0.1422442244224423</v>
       </c>
       <c r="M2">
-        <v>0.225</v>
+        <v>0.123</v>
       </c>
       <c r="N2">
-        <v>0.03348214285714286</v>
+        <v>0.02248628884826325</v>
       </c>
       <c r="O2">
-        <v>-0.1859504132231405</v>
+        <v>-0.2853828306264501</v>
       </c>
       <c r="P2">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0193452380952381</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.1074380165289256</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.095</v>
+        <v>0.123</v>
       </c>
       <c r="T2">
-        <v>0.4222222222222222</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.517</v>
+        <v>0.347</v>
       </c>
       <c r="V2">
-        <v>0.07693452380952381</v>
+        <v>0.06343692870201097</v>
       </c>
       <c r="W2">
-        <v>-0.1951612903225806</v>
+        <v>-0.06863057324840764</v>
       </c>
       <c r="X2">
-        <v>0.1293666052553338</v>
+        <v>0.2292940664259624</v>
       </c>
       <c r="Y2">
-        <v>-0.3245278955779144</v>
+        <v>-0.29792463967437</v>
       </c>
       <c r="Z2">
-        <v>0.2577614847061519</v>
+        <v>0.3017026784825251</v>
       </c>
       <c r="AA2">
-        <v>-0.1867338755871233</v>
+        <v>-0.05635766205317135</v>
       </c>
       <c r="AB2">
-        <v>0.08584449801508091</v>
+        <v>0.1429420632429382</v>
       </c>
       <c r="AC2">
-        <v>-0.2725783736022043</v>
+        <v>-0.1992997252961095</v>
       </c>
       <c r="AD2">
-        <v>5.03</v>
+        <v>5.09</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.03</v>
+        <v>5.09</v>
       </c>
       <c r="AG2">
-        <v>4.513</v>
+        <v>4.743</v>
       </c>
       <c r="AH2">
-        <v>0.4280851063829788</v>
+        <v>0.4820075757575758</v>
       </c>
       <c r="AI2">
-        <v>0.4841193455245428</v>
+        <v>0.4889529298751201</v>
       </c>
       <c r="AJ2">
-        <v>0.4017626635805217</v>
+        <v>0.4644081073142074</v>
       </c>
       <c r="AK2">
-        <v>0.4571052365035956</v>
+        <v>0.4713306171121932</v>
       </c>
       <c r="AL2">
-        <v>0.096</v>
+        <v>0.134</v>
       </c>
       <c r="AM2">
-        <v>0.096</v>
+        <v>0.134</v>
       </c>
       <c r="AN2">
-        <v>-3.183544303797468</v>
+        <v>-14.41926345609065</v>
       </c>
       <c r="AO2">
-        <v>-16.97916666666666</v>
+        <v>-4.223880597014925</v>
       </c>
       <c r="AP2">
-        <v>-2.85632911392405</v>
+        <v>-13.43626062322946</v>
       </c>
       <c r="AQ2">
-        <v>-16.97916666666666</v>
+        <v>-4.223880597014925</v>
       </c>
     </row>
     <row r="3">
@@ -715,116 +718,119 @@
           <t>Electronics (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.0408</v>
+      </c>
       <c r="G3">
-        <v>1.388888888888889</v>
+        <v>1.329042904290429</v>
       </c>
       <c r="H3">
-        <v>-0.4288888888888889</v>
+        <v>-0.1165016501650165</v>
       </c>
       <c r="I3">
-        <v>-0.7244444444444444</v>
+        <v>-0.1867986798679868</v>
       </c>
       <c r="J3">
-        <v>-0.7244444444444444</v>
+        <v>-0.1867986798679868</v>
       </c>
       <c r="K3">
-        <v>-1.21</v>
+        <v>-0.431</v>
       </c>
       <c r="L3">
-        <v>-0.5377777777777778</v>
+        <v>-0.1422442244224423</v>
       </c>
       <c r="M3">
-        <v>0.225</v>
+        <v>0.123</v>
       </c>
       <c r="N3">
-        <v>0.03348214285714286</v>
+        <v>0.02248628884826325</v>
       </c>
       <c r="O3">
-        <v>-0.1859504132231405</v>
+        <v>-0.2853828306264501</v>
       </c>
       <c r="P3">
-        <v>0.13</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0193452380952381</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.1074380165289256</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.095</v>
+        <v>0.123</v>
       </c>
       <c r="T3">
-        <v>0.4222222222222222</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.517</v>
+        <v>0.347</v>
       </c>
       <c r="V3">
-        <v>0.07693452380952381</v>
+        <v>0.06343692870201097</v>
       </c>
       <c r="W3">
-        <v>-0.1951612903225806</v>
+        <v>-0.06863057324840764</v>
       </c>
       <c r="X3">
-        <v>0.1293666052553338</v>
+        <v>0.2292940664259624</v>
       </c>
       <c r="Y3">
-        <v>-0.3245278955779144</v>
+        <v>-0.29792463967437</v>
       </c>
       <c r="Z3">
-        <v>0.2577614847061519</v>
+        <v>0.3017026784825251</v>
       </c>
       <c r="AA3">
-        <v>-0.1867338755871233</v>
+        <v>-0.05635766205317135</v>
       </c>
       <c r="AB3">
-        <v>0.08584449801508091</v>
+        <v>0.1429420632429382</v>
       </c>
       <c r="AC3">
-        <v>-0.2725783736022043</v>
+        <v>-0.1992997252961095</v>
       </c>
       <c r="AD3">
-        <v>5.03</v>
+        <v>5.09</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.03</v>
+        <v>5.09</v>
       </c>
       <c r="AG3">
-        <v>4.513</v>
+        <v>4.743</v>
       </c>
       <c r="AH3">
-        <v>0.4280851063829788</v>
+        <v>0.4820075757575758</v>
       </c>
       <c r="AI3">
-        <v>0.4841193455245428</v>
+        <v>0.4889529298751201</v>
       </c>
       <c r="AJ3">
-        <v>0.4017626635805217</v>
+        <v>0.4644081073142074</v>
       </c>
       <c r="AK3">
-        <v>0.4571052365035956</v>
+        <v>0.4713306171121932</v>
       </c>
       <c r="AL3">
-        <v>0.096</v>
+        <v>0.134</v>
       </c>
       <c r="AM3">
-        <v>0.096</v>
+        <v>0.134</v>
       </c>
       <c r="AN3">
-        <v>-3.183544303797468</v>
+        <v>-14.41926345609065</v>
       </c>
       <c r="AO3">
-        <v>-16.97916666666666</v>
+        <v>-4.223880597014925</v>
       </c>
       <c r="AP3">
-        <v>-2.85632911392405</v>
+        <v>-13.43626062322946</v>
       </c>
       <c r="AQ3">
-        <v>-16.97916666666666</v>
+        <v>-4.223880597014925</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_electronics_general.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0408</v>
+        <v>0.0394</v>
       </c>
       <c r="G2">
-        <v>1.329042904290429</v>
+        <v>0.07819148936170213</v>
       </c>
       <c r="H2">
-        <v>-0.1165016501650165</v>
+        <v>0.02446808510638298</v>
       </c>
       <c r="I2">
-        <v>-0.1867986798679868</v>
+        <v>-0.0627659574468085</v>
       </c>
       <c r="J2">
-        <v>-0.1867986798679868</v>
+        <v>-0.0627659574468085</v>
       </c>
       <c r="K2">
-        <v>-0.431</v>
+        <v>-0.232</v>
       </c>
       <c r="L2">
-        <v>-0.1422442244224423</v>
+        <v>-0.04113475177304965</v>
       </c>
       <c r="M2">
-        <v>0.123</v>
+        <v>0.016</v>
       </c>
       <c r="N2">
-        <v>0.02248628884826325</v>
+        <v>0.003524229074889868</v>
       </c>
       <c r="O2">
-        <v>-0.2853828306264501</v>
+        <v>-0.06896551724137931</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.123</v>
+        <v>0.016</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>0.347</v>
+        <v>0.123</v>
       </c>
       <c r="V2">
-        <v>0.06343692870201097</v>
+        <v>0.02709251101321586</v>
       </c>
       <c r="W2">
-        <v>-0.06863057324840764</v>
+        <v>-0.04621513944223108</v>
       </c>
       <c r="X2">
-        <v>0.2292940664259624</v>
+        <v>0.2215992978911712</v>
       </c>
       <c r="Y2">
-        <v>-0.29792463967437</v>
+        <v>-0.2678144373334023</v>
       </c>
       <c r="Z2">
-        <v>0.3017026784825251</v>
+        <v>0.5574224154971339</v>
       </c>
       <c r="AA2">
-        <v>-0.05635766205317135</v>
+        <v>-0.03498715161099031</v>
       </c>
       <c r="AB2">
-        <v>0.1429420632429382</v>
+        <v>0.1191009551275683</v>
       </c>
       <c r="AC2">
-        <v>-0.1992997252961095</v>
+        <v>-0.1540881067385587</v>
       </c>
       <c r="AD2">
-        <v>5.09</v>
+        <v>6.44</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.09</v>
+        <v>6.44</v>
       </c>
       <c r="AG2">
-        <v>4.743</v>
+        <v>6.317</v>
       </c>
       <c r="AH2">
-        <v>0.4820075757575758</v>
+        <v>0.5865209471766849</v>
       </c>
       <c r="AI2">
-        <v>0.4889529298751201</v>
+        <v>0.5849227974568574</v>
       </c>
       <c r="AJ2">
-        <v>0.4644081073142074</v>
+        <v>0.581836603113199</v>
       </c>
       <c r="AK2">
-        <v>0.4713306171121932</v>
+        <v>0.5802333057775328</v>
       </c>
       <c r="AL2">
-        <v>0.134</v>
+        <v>0.227</v>
       </c>
       <c r="AM2">
-        <v>0.134</v>
+        <v>0.227</v>
       </c>
       <c r="AN2">
-        <v>-14.41926345609065</v>
+        <v>-47.00729927007299</v>
       </c>
       <c r="AO2">
-        <v>-4.223880597014925</v>
+        <v>-1.559471365638766</v>
       </c>
       <c r="AP2">
-        <v>-13.43626062322946</v>
+        <v>-46.10948905109489</v>
       </c>
       <c r="AQ2">
-        <v>-4.223880597014925</v>
+        <v>-1.559471365638766</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0408</v>
+        <v>0.0394</v>
       </c>
       <c r="G3">
-        <v>1.329042904290429</v>
+        <v>0.07819148936170213</v>
       </c>
       <c r="H3">
-        <v>-0.1165016501650165</v>
+        <v>0.02446808510638298</v>
       </c>
       <c r="I3">
-        <v>-0.1867986798679868</v>
+        <v>-0.0627659574468085</v>
       </c>
       <c r="J3">
-        <v>-0.1867986798679868</v>
+        <v>-0.0627659574468085</v>
       </c>
       <c r="K3">
-        <v>-0.431</v>
+        <v>-0.232</v>
       </c>
       <c r="L3">
-        <v>-0.1422442244224423</v>
+        <v>-0.04113475177304965</v>
       </c>
       <c r="M3">
-        <v>0.123</v>
+        <v>0.016</v>
       </c>
       <c r="N3">
-        <v>0.02248628884826325</v>
+        <v>0.003524229074889868</v>
       </c>
       <c r="O3">
-        <v>-0.2853828306264501</v>
+        <v>-0.06896551724137931</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.123</v>
+        <v>0.016</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>0.347</v>
+        <v>0.123</v>
       </c>
       <c r="V3">
-        <v>0.06343692870201097</v>
+        <v>0.02709251101321586</v>
       </c>
       <c r="W3">
-        <v>-0.06863057324840764</v>
+        <v>-0.04621513944223108</v>
       </c>
       <c r="X3">
-        <v>0.2292940664259624</v>
+        <v>0.2215992978911712</v>
       </c>
       <c r="Y3">
-        <v>-0.29792463967437</v>
+        <v>-0.2678144373334023</v>
       </c>
       <c r="Z3">
-        <v>0.3017026784825251</v>
+        <v>0.5574224154971339</v>
       </c>
       <c r="AA3">
-        <v>-0.05635766205317135</v>
+        <v>-0.03498715161099031</v>
       </c>
       <c r="AB3">
-        <v>0.1429420632429382</v>
+        <v>0.1191009551275683</v>
       </c>
       <c r="AC3">
-        <v>-0.1992997252961095</v>
+        <v>-0.1540881067385587</v>
       </c>
       <c r="AD3">
-        <v>5.09</v>
+        <v>6.44</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.09</v>
+        <v>6.44</v>
       </c>
       <c r="AG3">
-        <v>4.743</v>
+        <v>6.317</v>
       </c>
       <c r="AH3">
-        <v>0.4820075757575758</v>
+        <v>0.5865209471766849</v>
       </c>
       <c r="AI3">
-        <v>0.4889529298751201</v>
+        <v>0.5849227974568574</v>
       </c>
       <c r="AJ3">
-        <v>0.4644081073142074</v>
+        <v>0.581836603113199</v>
       </c>
       <c r="AK3">
-        <v>0.4713306171121932</v>
+        <v>0.5802333057775328</v>
       </c>
       <c r="AL3">
-        <v>0.134</v>
+        <v>0.227</v>
       </c>
       <c r="AM3">
-        <v>0.134</v>
+        <v>0.227</v>
       </c>
       <c r="AN3">
-        <v>-14.41926345609065</v>
+        <v>-47.00729927007299</v>
       </c>
       <c r="AO3">
-        <v>-4.223880597014925</v>
+        <v>-1.559471365638766</v>
       </c>
       <c r="AP3">
-        <v>-13.43626062322946</v>
+        <v>-46.10948905109489</v>
       </c>
       <c r="AQ3">
-        <v>-4.223880597014925</v>
+        <v>-1.559471365638766</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_electronics_general.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,13 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1330128409987367</v>
+      </c>
+      <c r="C2">
+        <v>10.38606804504034</v>
+      </c>
+      <c r="D2">
+        <v>10.40696804504034</v>
       </c>
       <c r="E2">
-        <v>-6.63</v>
+        <v>-6.5101</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1199</v>
       </c>
       <c r="G2">
         <v>0.099</v>
@@ -1436,43 +1445,45 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02827242</v>
       </c>
       <c r="N2">
-        <v>-0.09899999999999992</v>
+        <v>-0.1272724199999999</v>
       </c>
       <c r="O2">
-        <v>-0.02474999999999998</v>
+        <v>-0.03181810499999998</v>
       </c>
       <c r="P2">
-        <v>-0.07424999999999994</v>
+        <v>-0.09545431499999993</v>
       </c>
       <c r="Q2">
-        <v>0.49075</v>
+        <v>0.469545685</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.1298895159750005</v>
+      </c>
+      <c r="T2">
+        <v>1.300838068462487</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-0.8754114433783871</v>
+      </c>
+      <c r="W2">
+        <v>0.4422220183486237</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-3.501645773513548</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1480,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1330128409987367</v>
+        <v>0.1349128409987367</v>
       </c>
       <c r="C3">
-        <v>10.38606804504034</v>
+        <v>10.04427814607665</v>
       </c>
       <c r="D3">
-        <v>10.40696804504034</v>
+        <v>10.18507814607665</v>
       </c>
       <c r="E3">
-        <v>-6.5101</v>
+        <v>-6.3902</v>
       </c>
       <c r="F3">
-        <v>0.1199</v>
+        <v>0.2398</v>
       </c>
       <c r="G3">
         <v>0.099</v>
@@ -1516,37 +1527,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M3">
-        <v>0.02827242</v>
+        <v>0.05654484000000001</v>
       </c>
       <c r="N3">
-        <v>-0.1272724199999999</v>
+        <v>-0.1555448399999999</v>
       </c>
       <c r="O3">
-        <v>-0.03181810499999998</v>
+        <v>-0.03888620999999998</v>
       </c>
       <c r="P3">
-        <v>-0.09545431499999993</v>
+        <v>-0.11665863</v>
       </c>
       <c r="Q3">
-        <v>0.469545685</v>
+        <v>0.44834137</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1298895159750005</v>
+        <v>0.1307475722604597</v>
       </c>
       <c r="T3">
-        <v>1.300838068462487</v>
+        <v>1.31411192630394</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-0.8754114433783871</v>
+        <v>-0.4377057216891935</v>
       </c>
       <c r="W3">
-        <v>0.4422220183486237</v>
+        <v>0.3390110091743119</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1554,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-3.501645773513548</v>
+        <v>-1.750822886756774</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1562,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1349128409987367</v>
+        <v>0.1368128409987367</v>
       </c>
       <c r="C4">
-        <v>10.04427814607665</v>
+        <v>9.711752671855772</v>
       </c>
       <c r="D4">
-        <v>10.18507814607665</v>
+        <v>9.972452671855772</v>
       </c>
       <c r="E4">
-        <v>-6.3902</v>
+        <v>-6.2703</v>
       </c>
       <c r="F4">
-        <v>0.2398</v>
+        <v>0.3597</v>
       </c>
       <c r="G4">
         <v>0.099</v>
@@ -1598,37 +1609,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M4">
-        <v>0.05654484000000001</v>
+        <v>0.08481726000000001</v>
       </c>
       <c r="N4">
-        <v>-0.1555448399999999</v>
+        <v>-0.1838172599999999</v>
       </c>
       <c r="O4">
-        <v>-0.03888620999999998</v>
+        <v>-0.04595431499999998</v>
       </c>
       <c r="P4">
-        <v>-0.11665863</v>
+        <v>-0.137862945</v>
       </c>
       <c r="Q4">
-        <v>0.44834137</v>
+        <v>0.427137055</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1307475722604597</v>
+        <v>0.1316233204280933</v>
       </c>
       <c r="T4">
-        <v>1.31411192630394</v>
+        <v>1.32765947193594</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-0.4377057216891935</v>
+        <v>-0.2918038144594624</v>
       </c>
       <c r="W4">
-        <v>0.3390110091743119</v>
+        <v>0.3046073394495412</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1636,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-1.750822886756774</v>
+        <v>-1.167215257837849</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1644,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1368128409987367</v>
+        <v>0.1387128409987367</v>
       </c>
       <c r="C5">
-        <v>9.711752671855772</v>
+        <v>9.387923270140636</v>
       </c>
       <c r="D5">
-        <v>9.972452671855772</v>
+        <v>9.768523270140635</v>
       </c>
       <c r="E5">
-        <v>-6.2703</v>
+        <v>-6.150399999999999</v>
       </c>
       <c r="F5">
-        <v>0.3597</v>
+        <v>0.4796</v>
       </c>
       <c r="G5">
         <v>0.099</v>
@@ -1680,37 +1691,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M5">
-        <v>0.08481726000000001</v>
+        <v>0.11308968</v>
       </c>
       <c r="N5">
-        <v>-0.1838172599999999</v>
+        <v>-0.2120896799999999</v>
       </c>
       <c r="O5">
-        <v>-0.04595431499999998</v>
+        <v>-0.05302241999999999</v>
       </c>
       <c r="P5">
-        <v>-0.137862945</v>
+        <v>-0.15906726</v>
       </c>
       <c r="Q5">
-        <v>0.427137055</v>
+        <v>0.40593274</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1316233204280933</v>
+        <v>0.1325173133492193</v>
       </c>
       <c r="T5">
-        <v>1.32765947193594</v>
+        <v>1.34148925810194</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.2918038144594624</v>
+        <v>-0.2188528608445968</v>
       </c>
       <c r="W5">
-        <v>0.3046073394495412</v>
+        <v>0.2874055045871559</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1718,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-1.167215257837849</v>
+        <v>-0.8754114433783873</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1726,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1387128409987367</v>
+        <v>0.1406128409987367</v>
       </c>
       <c r="C6">
-        <v>9.387923270140636</v>
+        <v>9.072267146626581</v>
       </c>
       <c r="D6">
-        <v>9.768523270140635</v>
+        <v>9.572767146626582</v>
       </c>
       <c r="E6">
-        <v>-6.150399999999999</v>
+        <v>-6.0305</v>
       </c>
       <c r="F6">
-        <v>0.4796</v>
+        <v>0.5995</v>
       </c>
       <c r="G6">
         <v>0.099</v>
@@ -1762,37 +1773,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M6">
-        <v>0.11308968</v>
+        <v>0.1413621</v>
       </c>
       <c r="N6">
-        <v>-0.2120896799999999</v>
+        <v>-0.2403620999999999</v>
       </c>
       <c r="O6">
-        <v>-0.05302241999999999</v>
+        <v>-0.06009052499999998</v>
       </c>
       <c r="P6">
-        <v>-0.15906726</v>
+        <v>-0.180271575</v>
       </c>
       <c r="Q6">
-        <v>0.40593274</v>
+        <v>0.384728425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1325173133492193</v>
+        <v>0.1334301271739479</v>
       </c>
       <c r="T6">
-        <v>1.34148925810194</v>
+        <v>1.355610197660907</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.2188528608445968</v>
+        <v>-0.1750822886756774</v>
       </c>
       <c r="W6">
-        <v>0.2874055045871559</v>
+        <v>0.2770844036697247</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1800,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-0.8754114433783873</v>
+        <v>-0.7003291547027097</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1808,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1406128409987367</v>
+        <v>0.1425128409987367</v>
       </c>
       <c r="C7">
-        <v>9.072267146626581</v>
+        <v>8.764302589833875</v>
       </c>
       <c r="D7">
-        <v>9.572767146626582</v>
+        <v>9.384702589833875</v>
       </c>
       <c r="E7">
-        <v>-6.0305</v>
+        <v>-5.9106</v>
       </c>
       <c r="F7">
-        <v>0.5995</v>
+        <v>0.7194</v>
       </c>
       <c r="G7">
         <v>0.099</v>
@@ -1844,37 +1855,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M7">
-        <v>0.1413621</v>
+        <v>0.16963452</v>
       </c>
       <c r="N7">
-        <v>-0.2403620999999999</v>
+        <v>-0.2686345199999999</v>
       </c>
       <c r="O7">
-        <v>-0.06009052499999998</v>
+        <v>-0.06715862999999998</v>
       </c>
       <c r="P7">
-        <v>-0.180271575</v>
+        <v>-0.2014758899999999</v>
       </c>
       <c r="Q7">
-        <v>0.384728425</v>
+        <v>0.36352411</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1334301271739479</v>
+        <v>0.1343623625694154</v>
       </c>
       <c r="T7">
-        <v>1.355610197660907</v>
+        <v>1.370031582742406</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.1750822886756774</v>
+        <v>-0.1459019072297312</v>
       </c>
       <c r="W7">
-        <v>0.2770844036697247</v>
+        <v>0.2702036697247706</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1882,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-0.7003291547027097</v>
+        <v>-0.5836076289189247</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1890,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1425128409987367</v>
+        <v>0.1444128409987367</v>
       </c>
       <c r="C8">
-        <v>8.764302589833877</v>
+        <v>8.463585013338815</v>
       </c>
       <c r="D8">
-        <v>9.384702589833877</v>
+        <v>9.203885013338814</v>
       </c>
       <c r="E8">
-        <v>-5.9106</v>
+        <v>-5.7907</v>
       </c>
       <c r="F8">
-        <v>0.7194</v>
+        <v>0.8392999999999999</v>
       </c>
       <c r="G8">
         <v>0.099</v>
@@ -1926,37 +1937,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M8">
-        <v>0.16963452</v>
+        <v>0.19790694</v>
       </c>
       <c r="N8">
-        <v>-0.2686345199999999</v>
+        <v>-0.29690694</v>
       </c>
       <c r="O8">
-        <v>-0.06715862999999998</v>
+        <v>-0.07422673499999999</v>
       </c>
       <c r="P8">
-        <v>-0.2014758899999999</v>
+        <v>-0.222680205</v>
       </c>
       <c r="Q8">
-        <v>0.36352411</v>
+        <v>0.342319795</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1343623625694154</v>
+        <v>0.1353146460379037</v>
       </c>
       <c r="T8">
-        <v>1.370031582742406</v>
+        <v>1.384763105137486</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.1459019072297312</v>
+        <v>-0.1250587776254839</v>
       </c>
       <c r="W8">
-        <v>0.2702036697247706</v>
+        <v>0.2652888597640891</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1964,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-0.5836076289189247</v>
+        <v>-0.5002351105019356</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1972,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1444128409987367</v>
+        <v>0.1463128409987367</v>
       </c>
       <c r="C9">
-        <v>8.463585013338818</v>
+        <v>8.169703446888381</v>
       </c>
       <c r="D9">
-        <v>9.203885013338818</v>
+        <v>9.029903446888381</v>
       </c>
       <c r="E9">
-        <v>-5.7907</v>
+        <v>-5.6708</v>
       </c>
       <c r="F9">
-        <v>0.8393</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="G9">
         <v>0.099</v>
@@ -2008,37 +2019,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M9">
-        <v>0.19790694</v>
+        <v>0.22617936</v>
       </c>
       <c r="N9">
-        <v>-0.29690694</v>
+        <v>-0.3251793599999999</v>
       </c>
       <c r="O9">
-        <v>-0.07422673499999999</v>
+        <v>-0.08129483999999998</v>
       </c>
       <c r="P9">
-        <v>-0.222680205</v>
+        <v>-0.2438845199999999</v>
       </c>
       <c r="Q9">
-        <v>0.342319795</v>
+        <v>0.32111548</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1353146460379037</v>
+        <v>0.1362876313209244</v>
       </c>
       <c r="T9">
-        <v>1.384763105137486</v>
+        <v>1.399814878019415</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.1250587776254839</v>
+        <v>-0.1094264304222984</v>
       </c>
       <c r="W9">
-        <v>0.2652888597640891</v>
+        <v>0.2616027522935779</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2046,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.5002351105019354</v>
+        <v>-0.4377057216891933</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2054,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1463128409987367</v>
+        <v>0.1482128409987367</v>
       </c>
       <c r="C10">
-        <v>8.169703446888381</v>
+        <v>7.882277418103575</v>
       </c>
       <c r="D10">
-        <v>9.029903446888381</v>
+        <v>8.862377418103575</v>
       </c>
       <c r="E10">
-        <v>-5.6708</v>
+        <v>-5.5509</v>
       </c>
       <c r="F10">
-        <v>0.9592000000000001</v>
+        <v>1.0791</v>
       </c>
       <c r="G10">
         <v>0.099</v>
@@ -2090,37 +2101,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M10">
-        <v>0.22617936</v>
+        <v>0.25445178</v>
       </c>
       <c r="N10">
-        <v>-0.3251793599999999</v>
+        <v>-0.3534517799999999</v>
       </c>
       <c r="O10">
-        <v>-0.08129483999999998</v>
+        <v>-0.08836294499999998</v>
       </c>
       <c r="P10">
-        <v>-0.2438845199999999</v>
+        <v>-0.265088835</v>
       </c>
       <c r="Q10">
-        <v>0.32111548</v>
+        <v>0.299911165</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1362876313209244</v>
+        <v>0.1372820008958796</v>
       </c>
       <c r="T10">
-        <v>1.399814878019415</v>
+        <v>1.415197459096551</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.1094264304222984</v>
+        <v>-0.09726793815315413</v>
       </c>
       <c r="W10">
-        <v>0.2616027522935779</v>
+        <v>0.2587357798165137</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2128,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.4377057216891933</v>
+        <v>-0.3890717526126164</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2136,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1482128409987367</v>
+        <v>0.1501128409987367</v>
       </c>
       <c r="C11">
-        <v>7.882277418103575</v>
+        <v>7.600954174970923</v>
       </c>
       <c r="D11">
-        <v>8.862377418103575</v>
+        <v>8.700954174970922</v>
       </c>
       <c r="E11">
-        <v>-5.5509</v>
+        <v>-5.431</v>
       </c>
       <c r="F11">
-        <v>1.0791</v>
+        <v>1.199</v>
       </c>
       <c r="G11">
         <v>0.099</v>
@@ -2172,37 +2183,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M11">
-        <v>0.25445178</v>
+        <v>0.2827242</v>
       </c>
       <c r="N11">
-        <v>-0.3534517799999999</v>
+        <v>-0.3817241999999999</v>
       </c>
       <c r="O11">
-        <v>-0.08836294499999998</v>
+        <v>-0.09543104999999998</v>
       </c>
       <c r="P11">
-        <v>-0.265088835</v>
+        <v>-0.2862931499999999</v>
       </c>
       <c r="Q11">
-        <v>0.299911165</v>
+        <v>0.27870685</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1372820008958796</v>
+        <v>0.1382984675725005</v>
       </c>
       <c r="T11">
-        <v>1.415197459096551</v>
+        <v>1.430921875308735</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.09726793815315413</v>
+        <v>-0.08754114433783872</v>
       </c>
       <c r="W11">
-        <v>0.2587357798165137</v>
+        <v>0.2564422018348624</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2210,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.3890717526126164</v>
+        <v>-0.3501645773513549</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2218,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1501128409987367</v>
+        <v>0.1520128409987367</v>
       </c>
       <c r="C12">
-        <v>7.600954174970923</v>
+        <v>7.325406206448535</v>
       </c>
       <c r="D12">
-        <v>8.700954174970922</v>
+        <v>8.545306206448535</v>
       </c>
       <c r="E12">
-        <v>-5.431</v>
+        <v>-5.3111</v>
       </c>
       <c r="F12">
-        <v>1.199</v>
+        <v>1.3189</v>
       </c>
       <c r="G12">
         <v>0.099</v>
@@ -2254,37 +2265,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M12">
-        <v>0.2827242</v>
+        <v>0.31099662</v>
       </c>
       <c r="N12">
-        <v>-0.3817242</v>
+        <v>-0.4099966199999999</v>
       </c>
       <c r="O12">
-        <v>-0.09543104999999999</v>
+        <v>-0.102499155</v>
       </c>
       <c r="P12">
-        <v>-0.28629315</v>
+        <v>-0.307497465</v>
       </c>
       <c r="Q12">
-        <v>0.27870685</v>
+        <v>0.257502535</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1382984675725005</v>
+        <v>0.1393377761969107</v>
       </c>
       <c r="T12">
-        <v>1.430921875308735</v>
+        <v>1.446999649188609</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.0875411443378387</v>
+        <v>-0.07958285848894428</v>
       </c>
       <c r="W12">
-        <v>0.2564422018348624</v>
+        <v>0.2545656380316931</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2292,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.3501645773513549</v>
+        <v>-0.3183314339557772</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2300,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1520128409987367</v>
+        <v>0.1539128409987367</v>
       </c>
       <c r="C13">
-        <v>7.325406206448535</v>
+        <v>7.055329024512842</v>
       </c>
       <c r="D13">
-        <v>8.545306206448535</v>
+        <v>8.395129024512842</v>
       </c>
       <c r="E13">
-        <v>-5.3111</v>
+        <v>-5.1912</v>
       </c>
       <c r="F13">
-        <v>1.3189</v>
+        <v>1.4388</v>
       </c>
       <c r="G13">
         <v>0.099</v>
@@ -2336,37 +2347,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M13">
-        <v>0.31099662</v>
+        <v>0.33926904</v>
       </c>
       <c r="N13">
-        <v>-0.4099966199999999</v>
+        <v>-0.4382690399999999</v>
       </c>
       <c r="O13">
-        <v>-0.102499155</v>
+        <v>-0.10956726</v>
       </c>
       <c r="P13">
-        <v>-0.307497465</v>
+        <v>-0.3287017799999999</v>
       </c>
       <c r="Q13">
-        <v>0.257502535</v>
+        <v>0.23629822</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1393377761969107</v>
+        <v>0.1404007054718755</v>
       </c>
       <c r="T13">
-        <v>1.446999649188609</v>
+        <v>1.463442827020297</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.07958285848894428</v>
+        <v>-0.07295095361486559</v>
       </c>
       <c r="W13">
-        <v>0.2545656380316931</v>
+        <v>0.2530018348623853</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2374,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.3183314339557772</v>
+        <v>-0.2918038144594624</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2382,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1539128409987367</v>
+        <v>0.1558128409987367</v>
       </c>
       <c r="C14">
-        <v>7.055329024512842</v>
+        <v>6.790439176039085</v>
       </c>
       <c r="D14">
-        <v>8.395129024512842</v>
+        <v>8.250139176039085</v>
       </c>
       <c r="E14">
-        <v>-5.1912</v>
+        <v>-5.0713</v>
       </c>
       <c r="F14">
-        <v>1.4388</v>
+        <v>1.5587</v>
       </c>
       <c r="G14">
         <v>0.099</v>
@@ -2418,37 +2429,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M14">
-        <v>0.33926904</v>
+        <v>0.36754146</v>
       </c>
       <c r="N14">
-        <v>-0.4382690399999999</v>
+        <v>-0.4665414599999999</v>
       </c>
       <c r="O14">
-        <v>-0.10956726</v>
+        <v>-0.116635365</v>
       </c>
       <c r="P14">
-        <v>-0.3287017799999999</v>
+        <v>-0.3499060949999999</v>
       </c>
       <c r="Q14">
-        <v>0.23629822</v>
+        <v>0.215093905</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1404007054718755</v>
+        <v>0.1414880699025867</v>
       </c>
       <c r="T14">
-        <v>1.463442827020297</v>
+        <v>1.480264008940071</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.07295095361486559</v>
+        <v>-0.06733934179833748</v>
       </c>
       <c r="W14">
-        <v>0.2530018348623853</v>
+        <v>0.251678616796048</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2456,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.2918038144594624</v>
+        <v>-0.2693573671933498</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2464,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1558128409987367</v>
+        <v>0.1577128409987367</v>
       </c>
       <c r="C15">
-        <v>6.790439176039085</v>
+        <v>6.530472457201596</v>
       </c>
       <c r="D15">
-        <v>8.250139176039085</v>
+        <v>8.110072457201596</v>
       </c>
       <c r="E15">
-        <v>-5.0713</v>
+        <v>-4.9514</v>
       </c>
       <c r="F15">
-        <v>1.5587</v>
+        <v>1.6786</v>
       </c>
       <c r="G15">
         <v>0.099</v>
@@ -2500,37 +2511,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M15">
-        <v>0.36754146</v>
+        <v>0.3958138800000001</v>
       </c>
       <c r="N15">
-        <v>-0.4665414599999999</v>
+        <v>-0.49481388</v>
       </c>
       <c r="O15">
-        <v>-0.116635365</v>
+        <v>-0.12370347</v>
       </c>
       <c r="P15">
-        <v>-0.3499060949999999</v>
+        <v>-0.37111041</v>
       </c>
       <c r="Q15">
-        <v>0.215093905</v>
+        <v>0.1938895899999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1414880699025867</v>
+        <v>0.1426007218781982</v>
       </c>
       <c r="T15">
-        <v>1.480264008940071</v>
+        <v>1.497476381137049</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.06733934179833748</v>
+        <v>-0.06252938881274193</v>
       </c>
       <c r="W15">
-        <v>0.251678616796048</v>
+        <v>0.2505444298820446</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2538,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.2693573671933498</v>
+        <v>-0.2501175552509678</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2546,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1577128409987367</v>
+        <v>0.1596128409987367</v>
       </c>
       <c r="C16">
-        <v>6.530472457201596</v>
+        <v>6.275182306727677</v>
       </c>
       <c r="D16">
-        <v>8.110072457201596</v>
+        <v>7.974682306727678</v>
       </c>
       <c r="E16">
-        <v>-4.9514</v>
+        <v>-4.8315</v>
       </c>
       <c r="F16">
-        <v>1.6786</v>
+        <v>1.7985</v>
       </c>
       <c r="G16">
         <v>0.099</v>
@@ -2582,37 +2593,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M16">
-        <v>0.3958138800000001</v>
+        <v>0.4240863000000001</v>
       </c>
       <c r="N16">
-        <v>-0.49481388</v>
+        <v>-0.5230863</v>
       </c>
       <c r="O16">
-        <v>-0.12370347</v>
+        <v>-0.130771575</v>
       </c>
       <c r="P16">
-        <v>-0.37111041</v>
+        <v>-0.392314725</v>
       </c>
       <c r="Q16">
-        <v>0.1938895899999999</v>
+        <v>0.172685275</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1426007218781982</v>
+        <v>0.1437395539002947</v>
       </c>
       <c r="T16">
-        <v>1.497476381137049</v>
+        <v>1.515093750326896</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.06252938881274193</v>
+        <v>-0.05836076289189247</v>
       </c>
       <c r="W16">
-        <v>0.2505444298820446</v>
+        <v>0.2495614678899083</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2620,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.2501175552509678</v>
+        <v>-0.2334430515675698</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2628,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1596128409987367</v>
+        <v>0.1615128409987367</v>
       </c>
       <c r="C17">
-        <v>6.275182306727682</v>
+        <v>6.024338357447685</v>
       </c>
       <c r="D17">
-        <v>7.974682306727681</v>
+        <v>7.843738357447685</v>
       </c>
       <c r="E17">
-        <v>-4.8315</v>
+        <v>-4.7116</v>
       </c>
       <c r="F17">
-        <v>1.7985</v>
+        <v>1.9184</v>
       </c>
       <c r="G17">
         <v>0.099</v>
@@ -2664,37 +2675,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M17">
-        <v>0.4240863</v>
+        <v>0.45235872</v>
       </c>
       <c r="N17">
-        <v>-0.5230862999999999</v>
+        <v>-0.55135872</v>
       </c>
       <c r="O17">
-        <v>-0.130771575</v>
+        <v>-0.13783968</v>
       </c>
       <c r="P17">
-        <v>-0.3923147249999999</v>
+        <v>-0.4135190399999999</v>
       </c>
       <c r="Q17">
-        <v>0.172685275</v>
+        <v>0.15148096</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1437395539002947</v>
+        <v>0.1449055009705363</v>
       </c>
       <c r="T17">
-        <v>1.515093750326896</v>
+        <v>1.533130580687931</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.05836076289189247</v>
+        <v>-0.05471321521114919</v>
       </c>
       <c r="W17">
-        <v>0.2495614678899083</v>
+        <v>0.248701376146789</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2702,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.2334430515675698</v>
+        <v>-0.2188528608445968</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2710,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1615128409987367</v>
+        <v>0.1634128409987367</v>
       </c>
       <c r="C18">
-        <v>6.024338357447685</v>
+        <v>5.777725128240762</v>
       </c>
       <c r="D18">
-        <v>7.843738357447685</v>
+        <v>7.717025128240762</v>
       </c>
       <c r="E18">
-        <v>-4.7116</v>
+        <v>-4.591699999999999</v>
       </c>
       <c r="F18">
-        <v>1.9184</v>
+        <v>2.0383</v>
       </c>
       <c r="G18">
         <v>0.099</v>
@@ -2746,37 +2757,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M18">
-        <v>0.45235872</v>
+        <v>0.48063114</v>
       </c>
       <c r="N18">
-        <v>-0.55135872</v>
+        <v>-0.5796311399999999</v>
       </c>
       <c r="O18">
-        <v>-0.13783968</v>
+        <v>-0.144907785</v>
       </c>
       <c r="P18">
-        <v>-0.4135190399999999</v>
+        <v>-0.4347233549999999</v>
       </c>
       <c r="Q18">
-        <v>0.15148096</v>
+        <v>0.130276645</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1449055009705363</v>
+        <v>0.1460995431509042</v>
       </c>
       <c r="T18">
-        <v>1.533130580687931</v>
+        <v>1.551602033467303</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.05471321521114919</v>
+        <v>-0.05149479078696395</v>
       </c>
       <c r="W18">
-        <v>0.248701376146789</v>
+        <v>0.2479424716675661</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2784,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.2188528608445968</v>
+        <v>-0.2059791631478558</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2792,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1634128409987367</v>
+        <v>0.1653128409987367</v>
       </c>
       <c r="C19">
-        <v>5.777725128240762</v>
+        <v>5.535140840752254</v>
       </c>
       <c r="D19">
-        <v>7.717025128240762</v>
+        <v>7.594340840752253</v>
       </c>
       <c r="E19">
-        <v>-4.591699999999999</v>
+        <v>-4.4718</v>
       </c>
       <c r="F19">
-        <v>2.0383</v>
+        <v>2.1582</v>
       </c>
       <c r="G19">
         <v>0.099</v>
@@ -2828,37 +2839,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M19">
-        <v>0.48063114</v>
+        <v>0.5089035600000001</v>
       </c>
       <c r="N19">
-        <v>-0.5796311399999999</v>
+        <v>-0.60790356</v>
       </c>
       <c r="O19">
-        <v>-0.144907785</v>
+        <v>-0.15197589</v>
       </c>
       <c r="P19">
-        <v>-0.4347233549999999</v>
+        <v>-0.45592767</v>
       </c>
       <c r="Q19">
-        <v>0.130276645</v>
+        <v>0.1090723299999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1460995431509042</v>
+        <v>0.1473227083112811</v>
       </c>
       <c r="T19">
-        <v>1.551602033467303</v>
+        <v>1.570524009485197</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.05149479078696395</v>
+        <v>-0.04863396907657705</v>
       </c>
       <c r="W19">
-        <v>0.2479424716675661</v>
+        <v>0.2472678899082569</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2866,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.2059791631478558</v>
+        <v>-0.1945358763063081</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2874,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1653128409987367</v>
+        <v>0.1672128409987367</v>
       </c>
       <c r="C20">
-        <v>5.535140840752251</v>
+        <v>5.296396347214872</v>
       </c>
       <c r="D20">
-        <v>7.594340840752251</v>
+        <v>7.475496347214872</v>
       </c>
       <c r="E20">
-        <v>-4.4718</v>
+        <v>-4.3519</v>
       </c>
       <c r="F20">
-        <v>2.1582</v>
+        <v>2.2781</v>
       </c>
       <c r="G20">
         <v>0.099</v>
@@ -2910,37 +2921,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M20">
-        <v>0.50890356</v>
+        <v>0.5371759800000001</v>
       </c>
       <c r="N20">
-        <v>-0.60790356</v>
+        <v>-0.63617598</v>
       </c>
       <c r="O20">
-        <v>-0.15197589</v>
+        <v>-0.159043995</v>
       </c>
       <c r="P20">
-        <v>-0.45592767</v>
+        <v>-0.477131985</v>
       </c>
       <c r="Q20">
-        <v>0.1090723299999999</v>
+        <v>0.08786801499999997</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1473227083112811</v>
+        <v>0.1485760750805561</v>
       </c>
       <c r="T20">
-        <v>1.570524009485197</v>
+        <v>1.589913194787484</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.04863396907657706</v>
+        <v>-0.04607428649359931</v>
       </c>
       <c r="W20">
-        <v>0.2472678899082569</v>
+        <v>0.2466643167551907</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2948,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.1945358763063083</v>
+        <v>-0.1842971459743972</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2956,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1672128409987367</v>
+        <v>0.1691128409987367</v>
       </c>
       <c r="C21">
-        <v>5.296396347214872</v>
+        <v>5.061314157390425</v>
       </c>
       <c r="D21">
-        <v>7.475496347214872</v>
+        <v>7.360314157390425</v>
       </c>
       <c r="E21">
-        <v>-4.3519</v>
+        <v>-4.231999999999999</v>
       </c>
       <c r="F21">
-        <v>2.2781</v>
+        <v>2.398</v>
       </c>
       <c r="G21">
         <v>0.099</v>
@@ -2992,37 +3003,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M21">
-        <v>0.5371759800000001</v>
+        <v>0.5654484000000001</v>
       </c>
       <c r="N21">
-        <v>-0.63617598</v>
+        <v>-0.6644483999999999</v>
       </c>
       <c r="O21">
-        <v>-0.159043995</v>
+        <v>-0.1661121</v>
       </c>
       <c r="P21">
-        <v>-0.477131985</v>
+        <v>-0.4983363</v>
       </c>
       <c r="Q21">
-        <v>0.08786801499999997</v>
+        <v>0.06666369999999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1485760750805561</v>
+        <v>0.1498607760190631</v>
       </c>
       <c r="T21">
-        <v>1.589913194787484</v>
+        <v>1.609787109722327</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.04607428649359931</v>
+        <v>-0.04377057216891935</v>
       </c>
       <c r="W21">
-        <v>0.2466643167551907</v>
+        <v>0.2461211009174312</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3030,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.1842971459743972</v>
+        <v>-0.1750822886756773</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3038,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1691128409987367</v>
+        <v>0.1710128409987367</v>
       </c>
       <c r="C22">
-        <v>5.061314157390425</v>
+        <v>4.829727554103604</v>
       </c>
       <c r="D22">
-        <v>7.360314157390425</v>
+        <v>7.248627554103604</v>
       </c>
       <c r="E22">
-        <v>-4.231999999999999</v>
+        <v>-4.1121</v>
       </c>
       <c r="F22">
-        <v>2.398</v>
+        <v>2.5179</v>
       </c>
       <c r="G22">
         <v>0.099</v>
@@ -3074,37 +3085,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M22">
-        <v>0.5654484000000001</v>
+        <v>0.5937208200000001</v>
       </c>
       <c r="N22">
-        <v>-0.6644483999999999</v>
+        <v>-0.6927208200000001</v>
       </c>
       <c r="O22">
-        <v>-0.1661121</v>
+        <v>-0.173180205</v>
       </c>
       <c r="P22">
-        <v>-0.4983363</v>
+        <v>-0.5195406150000001</v>
       </c>
       <c r="Q22">
-        <v>0.06666369999999999</v>
+        <v>0.0454593849999998</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1498607760190631</v>
+        <v>0.1511780010319626</v>
       </c>
       <c r="T22">
-        <v>1.609787109722327</v>
+        <v>1.630164161744129</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.04377057216891935</v>
+        <v>-0.04168625920849461</v>
       </c>
       <c r="W22">
-        <v>0.2461211009174312</v>
+        <v>0.245629619921363</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3112,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.1750822886756773</v>
+        <v>-0.1667450368339785</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3120,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1710128409987367</v>
+        <v>0.1729128409987367</v>
       </c>
       <c r="C23">
-        <v>4.829727554103604</v>
+        <v>4.601479788098329</v>
       </c>
       <c r="D23">
-        <v>7.248627554103604</v>
+        <v>7.140279788098328</v>
       </c>
       <c r="E23">
-        <v>-4.1121</v>
+        <v>-3.9922</v>
       </c>
       <c r="F23">
-        <v>2.5179</v>
+        <v>2.6378</v>
       </c>
       <c r="G23">
         <v>0.099</v>
@@ -3156,37 +3167,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M23">
-        <v>0.59372082</v>
+        <v>0.62199324</v>
       </c>
       <c r="N23">
-        <v>-0.6927208199999999</v>
+        <v>-0.7209932399999999</v>
       </c>
       <c r="O23">
-        <v>-0.173180205</v>
+        <v>-0.18024831</v>
       </c>
       <c r="P23">
-        <v>-0.5195406149999999</v>
+        <v>-0.5407449299999999</v>
       </c>
       <c r="Q23">
-        <v>0.04545938500000002</v>
+        <v>0.02425507000000005</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1511780010319626</v>
+        <v>0.1525290010451929</v>
       </c>
       <c r="T23">
-        <v>1.630164161744129</v>
+        <v>1.65106370227931</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.04168625920849462</v>
+        <v>-0.03979142924447214</v>
       </c>
       <c r="W23">
-        <v>0.245629619921363</v>
+        <v>0.2451828190158465</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3194,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.1667450368339785</v>
+        <v>-0.1591657169778884</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3202,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1729128409987367</v>
+        <v>0.1748128409987367</v>
       </c>
       <c r="C24">
-        <v>4.601479788098329</v>
+        <v>4.376423344039246</v>
       </c>
       <c r="D24">
-        <v>7.140279788098328</v>
+        <v>7.035123344039246</v>
       </c>
       <c r="E24">
-        <v>-3.9922</v>
+        <v>-3.8723</v>
       </c>
       <c r="F24">
-        <v>2.6378</v>
+        <v>2.7577</v>
       </c>
       <c r="G24">
         <v>0.099</v>
@@ -3238,37 +3249,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M24">
-        <v>0.62199324</v>
+        <v>0.6502656600000001</v>
       </c>
       <c r="N24">
-        <v>-0.7209932399999999</v>
+        <v>-0.7492656600000001</v>
       </c>
       <c r="O24">
-        <v>-0.18024831</v>
+        <v>-0.187316415</v>
       </c>
       <c r="P24">
-        <v>-0.5407449299999999</v>
+        <v>-0.5619492450000001</v>
       </c>
       <c r="Q24">
-        <v>0.02425507000000005</v>
+        <v>0.00305075499999985</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1525290010451929</v>
+        <v>0.1539150919678578</v>
       </c>
       <c r="T24">
-        <v>1.65106370227931</v>
+        <v>1.672506088023197</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.03979142924447214</v>
+        <v>-0.03806136710340813</v>
       </c>
       <c r="W24">
-        <v>0.2451828190158465</v>
+        <v>0.2447748703629837</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3276,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.1591657169778884</v>
+        <v>-0.1522454684136325</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3284,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1748128409987367</v>
+        <v>0.1767128409987367</v>
       </c>
       <c r="C25">
-        <v>4.376423344039246</v>
+        <v>4.154419270430428</v>
       </c>
       <c r="D25">
-        <v>7.035123344039246</v>
+        <v>6.933019270430428</v>
       </c>
       <c r="E25">
-        <v>-3.8723</v>
+        <v>-3.7524</v>
       </c>
       <c r="F25">
-        <v>2.7577</v>
+        <v>2.8776</v>
       </c>
       <c r="G25">
         <v>0.099</v>
@@ -3320,37 +3331,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M25">
-        <v>0.6502656600000001</v>
+        <v>0.67853808</v>
       </c>
       <c r="N25">
-        <v>-0.7492656600000001</v>
+        <v>-0.77753808</v>
       </c>
       <c r="O25">
-        <v>-0.187316415</v>
+        <v>-0.19438452</v>
       </c>
       <c r="P25">
-        <v>-0.5619492450000001</v>
+        <v>-0.58315356</v>
       </c>
       <c r="Q25">
-        <v>0.00305075499999985</v>
+        <v>-0.01815356000000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1539150919678578</v>
+        <v>0.1553376589674348</v>
       </c>
       <c r="T25">
-        <v>1.672506088023197</v>
+        <v>1.694512747076134</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.03806136710340813</v>
+        <v>-0.03647547680743279</v>
       </c>
       <c r="W25">
-        <v>0.2447748703629837</v>
+        <v>0.2444009174311927</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3358,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.1522454684136325</v>
+        <v>-0.1459019072297312</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3366,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1767128409987367</v>
+        <v>0.1786128409987367</v>
       </c>
       <c r="C26">
-        <v>4.154419270430428</v>
+        <v>3.935336567050542</v>
       </c>
       <c r="D26">
-        <v>6.933019270430428</v>
+        <v>6.833836567050542</v>
       </c>
       <c r="E26">
-        <v>-3.7524</v>
+        <v>-3.6325</v>
       </c>
       <c r="F26">
-        <v>2.8776</v>
+        <v>2.9975</v>
       </c>
       <c r="G26">
         <v>0.099</v>
@@ -3402,37 +3413,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M26">
-        <v>0.67853808</v>
+        <v>0.7068105</v>
       </c>
       <c r="N26">
-        <v>-0.77753808</v>
+        <v>-0.8058105</v>
       </c>
       <c r="O26">
-        <v>-0.19438452</v>
+        <v>-0.201452625</v>
       </c>
       <c r="P26">
-        <v>-0.58315356</v>
+        <v>-0.604357875</v>
       </c>
       <c r="Q26">
-        <v>-0.01815356000000001</v>
+        <v>-0.0393578750000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1553376589674348</v>
+        <v>0.1567981610870006</v>
       </c>
       <c r="T26">
-        <v>1.694512747076134</v>
+        <v>1.717106250370482</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.03647547680743279</v>
+        <v>-0.03501645773513549</v>
       </c>
       <c r="W26">
-        <v>0.2444009174311927</v>
+        <v>0.244056880733945</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3440,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.1459019072297312</v>
+        <v>-0.140065830940542</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3448,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1786128409987367</v>
+        <v>0.1805128409987367</v>
       </c>
       <c r="C27">
-        <v>3.935336567050542</v>
+        <v>3.719051624225991</v>
       </c>
       <c r="D27">
-        <v>6.833836567050542</v>
+        <v>6.737451624225991</v>
       </c>
       <c r="E27">
-        <v>-3.6325</v>
+        <v>-3.5126</v>
       </c>
       <c r="F27">
-        <v>2.9975</v>
+        <v>3.1174</v>
       </c>
       <c r="G27">
         <v>0.099</v>
@@ -3484,37 +3495,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M27">
-        <v>0.7068105</v>
+        <v>0.73508292</v>
       </c>
       <c r="N27">
-        <v>-0.8058105</v>
+        <v>-0.8340829199999999</v>
       </c>
       <c r="O27">
-        <v>-0.201452625</v>
+        <v>-0.20852073</v>
       </c>
       <c r="P27">
-        <v>-0.604357875</v>
+        <v>-0.6255621899999999</v>
       </c>
       <c r="Q27">
-        <v>-0.0393578750000001</v>
+        <v>-0.06056218999999996</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1567981610870006</v>
+        <v>0.158298136236825</v>
       </c>
       <c r="T27">
-        <v>1.717106250370482</v>
+        <v>1.740310388889002</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.03501645773513549</v>
+        <v>-0.03366967089916874</v>
       </c>
       <c r="W27">
-        <v>0.244056880733945</v>
+        <v>0.243739308398024</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3522,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.140065830940542</v>
+        <v>-0.1346786835966751</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3530,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1805128409987367</v>
+        <v>0.1824128409987367</v>
       </c>
       <c r="C28">
-        <v>3.719051624225991</v>
+        <v>3.505447708895312</v>
       </c>
       <c r="D28">
-        <v>6.737451624225991</v>
+        <v>6.643747708895312</v>
       </c>
       <c r="E28">
-        <v>-3.5126</v>
+        <v>-3.3927</v>
       </c>
       <c r="F28">
-        <v>3.1174</v>
+        <v>3.2373</v>
       </c>
       <c r="G28">
         <v>0.099</v>
@@ -3566,37 +3577,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M28">
-        <v>0.73508292</v>
+        <v>0.76335534</v>
       </c>
       <c r="N28">
-        <v>-0.8340829199999999</v>
+        <v>-0.8623553399999999</v>
       </c>
       <c r="O28">
-        <v>-0.20852073</v>
+        <v>-0.215588835</v>
       </c>
       <c r="P28">
-        <v>-0.6255621899999999</v>
+        <v>-0.646766505</v>
       </c>
       <c r="Q28">
-        <v>-0.06056218999999996</v>
+        <v>-0.08176650500000004</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.158298136236825</v>
+        <v>0.1598392065962335</v>
       </c>
       <c r="T28">
-        <v>1.740310388889002</v>
+        <v>1.764150257229948</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.03366967089916874</v>
+        <v>-0.03242264605105137</v>
       </c>
       <c r="W28">
-        <v>0.243739308398024</v>
+        <v>0.2434452599388379</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3604,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.1346786835966751</v>
+        <v>-0.1296905842042053</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3612,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1824128409987367</v>
+        <v>0.1843128409987367</v>
       </c>
       <c r="C29">
-        <v>3.505447708895312</v>
+        <v>3.294414492971911</v>
       </c>
       <c r="D29">
-        <v>6.643747708895312</v>
+        <v>6.552614492971911</v>
       </c>
       <c r="E29">
-        <v>-3.3927</v>
+        <v>-3.2728</v>
       </c>
       <c r="F29">
-        <v>3.2373</v>
+        <v>3.3572</v>
       </c>
       <c r="G29">
         <v>0.099</v>
@@ -3648,37 +3659,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M29">
-        <v>0.76335534</v>
+        <v>0.7916277600000001</v>
       </c>
       <c r="N29">
-        <v>-0.8623553399999999</v>
+        <v>-0.8906277600000001</v>
       </c>
       <c r="O29">
-        <v>-0.215588835</v>
+        <v>-0.22265694</v>
       </c>
       <c r="P29">
-        <v>-0.646766505</v>
+        <v>-0.6679708200000001</v>
       </c>
       <c r="Q29">
-        <v>-0.08176650500000004</v>
+        <v>-0.1029708200000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1598392065962335</v>
+        <v>0.1614230844656257</v>
       </c>
       <c r="T29">
-        <v>1.764150257229948</v>
+        <v>1.788652344135919</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.03242264605105137</v>
+        <v>-0.03126469440637097</v>
       </c>
       <c r="W29">
-        <v>0.2434452599388379</v>
+        <v>0.2431722149410223</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3686,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.1296905842042053</v>
+        <v>-0.1250587776254839</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3694,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1843128409987367</v>
+        <v>0.1862128409987367</v>
       </c>
       <c r="C30">
-        <v>3.294414492971911</v>
+        <v>3.085847619998673</v>
       </c>
       <c r="D30">
-        <v>6.552614492971911</v>
+        <v>6.463947619998673</v>
       </c>
       <c r="E30">
-        <v>-3.2728</v>
+        <v>-3.152899999999999</v>
       </c>
       <c r="F30">
-        <v>3.3572</v>
+        <v>3.477100000000001</v>
       </c>
       <c r="G30">
         <v>0.099</v>
@@ -3730,37 +3741,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M30">
-        <v>0.7916277600000001</v>
+        <v>0.8199001800000002</v>
       </c>
       <c r="N30">
-        <v>-0.8906277600000001</v>
+        <v>-0.9189001800000001</v>
       </c>
       <c r="O30">
-        <v>-0.22265694</v>
+        <v>-0.229725045</v>
       </c>
       <c r="P30">
-        <v>-0.6679708200000001</v>
+        <v>-0.689175135</v>
       </c>
       <c r="Q30">
-        <v>-0.1029708200000001</v>
+        <v>-0.1241751350000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1614230844656257</v>
+        <v>0.1630515786130288</v>
       </c>
       <c r="T30">
-        <v>1.788652344135919</v>
+        <v>1.813844630673045</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.03126469440637097</v>
+        <v>-0.03018660149580644</v>
       </c>
       <c r="W30">
-        <v>0.2431722149410223</v>
+        <v>0.2429180006327112</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3768,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.1250587776254839</v>
+        <v>-0.1207464059832257</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3776,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1862128409987367</v>
+        <v>0.1881128409987367</v>
       </c>
       <c r="C31">
-        <v>3.085847619998674</v>
+        <v>2.879648306515737</v>
       </c>
       <c r="D31">
-        <v>6.463947619998673</v>
+        <v>6.377648306515737</v>
       </c>
       <c r="E31">
-        <v>-3.1529</v>
+        <v>-3.033</v>
       </c>
       <c r="F31">
-        <v>3.4771</v>
+        <v>3.597</v>
       </c>
       <c r="G31">
         <v>0.099</v>
@@ -3812,37 +3823,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M31">
-        <v>0.81990018</v>
+        <v>0.8481726000000001</v>
       </c>
       <c r="N31">
-        <v>-0.9189001799999998</v>
+        <v>-0.9471726</v>
       </c>
       <c r="O31">
-        <v>-0.229725045</v>
+        <v>-0.23679315</v>
       </c>
       <c r="P31">
-        <v>-0.6891751349999999</v>
+        <v>-0.71037945</v>
       </c>
       <c r="Q31">
-        <v>-0.124175135</v>
+        <v>-0.1453794500000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1630515786130288</v>
+        <v>0.1647266011646435</v>
       </c>
       <c r="T31">
-        <v>1.813844630673045</v>
+        <v>1.839756696825517</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.03018660149580646</v>
+        <v>-0.02918038144594624</v>
       </c>
       <c r="W31">
-        <v>0.2429180006327112</v>
+        <v>0.2426807339449541</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3850,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.1207464059832257</v>
+        <v>-0.116721525783785</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3858,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1881128409987367</v>
+        <v>0.1900128409987367</v>
       </c>
       <c r="C32">
-        <v>2.879648306515737</v>
+        <v>2.675722974940124</v>
       </c>
       <c r="D32">
-        <v>6.377648306515737</v>
+        <v>6.293622974940123</v>
       </c>
       <c r="E32">
-        <v>-3.033</v>
+        <v>-2.9131</v>
       </c>
       <c r="F32">
-        <v>3.597</v>
+        <v>3.7169</v>
       </c>
       <c r="G32">
         <v>0.099</v>
@@ -3894,37 +3905,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M32">
-        <v>0.8481726000000001</v>
+        <v>0.87644502</v>
       </c>
       <c r="N32">
-        <v>-0.9471726</v>
+        <v>-0.97544502</v>
       </c>
       <c r="O32">
-        <v>-0.23679315</v>
+        <v>-0.243861255</v>
       </c>
       <c r="P32">
-        <v>-0.71037945</v>
+        <v>-0.731583765</v>
       </c>
       <c r="Q32">
-        <v>-0.1453794500000001</v>
+        <v>-0.1665837650000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1647266011646435</v>
+        <v>0.1664501750945659</v>
       </c>
       <c r="T32">
-        <v>1.839756696825517</v>
+        <v>1.86641983735922</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.02918038144594624</v>
+        <v>-0.02823907881865765</v>
       </c>
       <c r="W32">
-        <v>0.2426807339449541</v>
+        <v>0.2424587747854395</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3932,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.116721525783785</v>
+        <v>-0.1129563152746307</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3940,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1900128409987367</v>
+        <v>0.1919128409987367</v>
       </c>
       <c r="C33">
-        <v>2.675722974940124</v>
+        <v>2.47398291508878</v>
       </c>
       <c r="D33">
-        <v>6.293622974940123</v>
+        <v>6.21178291508878</v>
       </c>
       <c r="E33">
-        <v>-2.9131</v>
+        <v>-2.7932</v>
       </c>
       <c r="F33">
-        <v>3.7169</v>
+        <v>3.8368</v>
       </c>
       <c r="G33">
         <v>0.099</v>
@@ -3976,37 +3987,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M33">
-        <v>0.87644502</v>
+        <v>0.9047174400000001</v>
       </c>
       <c r="N33">
-        <v>-0.97544502</v>
+        <v>-1.00371744</v>
       </c>
       <c r="O33">
-        <v>-0.243861255</v>
+        <v>-0.25092936</v>
       </c>
       <c r="P33">
-        <v>-0.731583765</v>
+        <v>-0.75278808</v>
       </c>
       <c r="Q33">
-        <v>-0.1665837650000001</v>
+        <v>-0.18778808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1664501750945659</v>
+        <v>0.1682244423753683</v>
       </c>
       <c r="T33">
-        <v>1.86641983735922</v>
+        <v>1.89386718790862</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.02823907881865765</v>
+        <v>-0.0273566076055746</v>
       </c>
       <c r="W33">
-        <v>0.2424587747854395</v>
+        <v>0.2422506880733945</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4014,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.1129563152746307</v>
+        <v>-0.1094264304222983</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4022,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1919128409987367</v>
+        <v>0.1938128409987367</v>
       </c>
       <c r="C34">
-        <v>2.47398291508878</v>
+        <v>2.274343971771227</v>
       </c>
       <c r="D34">
-        <v>6.21178291508878</v>
+        <v>6.132043971771227</v>
       </c>
       <c r="E34">
-        <v>-2.7932</v>
+        <v>-2.6733</v>
       </c>
       <c r="F34">
-        <v>3.8368</v>
+        <v>3.9567</v>
       </c>
       <c r="G34">
         <v>0.099</v>
@@ -4058,37 +4069,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M34">
-        <v>0.9047174400000001</v>
+        <v>0.9329898600000001</v>
       </c>
       <c r="N34">
-        <v>-1.00371744</v>
+        <v>-1.03198986</v>
       </c>
       <c r="O34">
-        <v>-0.25092936</v>
+        <v>-0.257997465</v>
       </c>
       <c r="P34">
-        <v>-0.75278808</v>
+        <v>-0.7739923949999999</v>
       </c>
       <c r="Q34">
-        <v>-0.18778808</v>
+        <v>-0.208992395</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1682244423753683</v>
+        <v>0.1700516728585828</v>
       </c>
       <c r="T34">
-        <v>1.89386718790862</v>
+        <v>1.922133862355017</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.0273566076055746</v>
+        <v>-0.02652761949631476</v>
       </c>
       <c r="W34">
-        <v>0.2422506880733945</v>
+        <v>0.242055212677231</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4096,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.1094264304222983</v>
+        <v>-0.1061104779852591</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4104,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1938128409987367</v>
+        <v>0.1957128409987367</v>
       </c>
       <c r="C35">
-        <v>2.274343971771227</v>
+        <v>2.076726256138957</v>
       </c>
       <c r="D35">
-        <v>6.132043971771227</v>
+        <v>6.054326256138957</v>
       </c>
       <c r="E35">
-        <v>-2.6733</v>
+        <v>-2.5534</v>
       </c>
       <c r="F35">
-        <v>3.9567</v>
+        <v>4.0766</v>
       </c>
       <c r="G35">
         <v>0.099</v>
@@ -4140,37 +4151,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M35">
-        <v>0.9329898600000001</v>
+        <v>0.96126228</v>
       </c>
       <c r="N35">
-        <v>-1.03198986</v>
+        <v>-1.06026228</v>
       </c>
       <c r="O35">
-        <v>-0.257997465</v>
+        <v>-0.26506557</v>
       </c>
       <c r="P35">
-        <v>-0.7739923949999999</v>
+        <v>-0.7951967099999999</v>
       </c>
       <c r="Q35">
-        <v>-0.208992395</v>
+        <v>-0.23019671</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1700516728585828</v>
+        <v>0.1719342739625007</v>
       </c>
       <c r="T35">
-        <v>1.922133862355017</v>
+        <v>1.95125710269373</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.02652761949631476</v>
+        <v>-0.02574739539348198</v>
       </c>
       <c r="W35">
-        <v>0.242055212677231</v>
+        <v>0.2418712358337831</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4178,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.1061104779852591</v>
+        <v>-0.1029895815739279</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4186,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1957128409987367</v>
+        <v>0.1976128409987367</v>
       </c>
       <c r="C36">
-        <v>2.076726256138957</v>
+        <v>1.881053878710358</v>
       </c>
       <c r="D36">
-        <v>6.054326256138957</v>
+        <v>5.978553878710358</v>
       </c>
       <c r="E36">
-        <v>-2.5534</v>
+        <v>-2.4335</v>
       </c>
       <c r="F36">
-        <v>4.0766</v>
+        <v>4.1965</v>
       </c>
       <c r="G36">
         <v>0.099</v>
@@ -4222,37 +4233,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M36">
-        <v>0.96126228</v>
+        <v>0.9895347000000001</v>
       </c>
       <c r="N36">
-        <v>-1.06026228</v>
+        <v>-1.0885347</v>
       </c>
       <c r="O36">
-        <v>-0.26506557</v>
+        <v>-0.272133675</v>
       </c>
       <c r="P36">
-        <v>-0.7951967099999999</v>
+        <v>-0.816401025</v>
       </c>
       <c r="Q36">
-        <v>-0.23019671</v>
+        <v>-0.2514010250000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1719342739625007</v>
+        <v>0.1738748012542315</v>
       </c>
       <c r="T36">
-        <v>1.95125710269373</v>
+        <v>1.981276442735172</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.02574739539348198</v>
+        <v>-0.02501175552509677</v>
       </c>
       <c r="W36">
-        <v>0.2418712358337831</v>
+        <v>0.2416977719528178</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4260,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.1029895815739279</v>
+        <v>-0.1000470221003871</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4268,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1976128409987367</v>
+        <v>0.1995128409987367</v>
       </c>
       <c r="C37">
-        <v>1.881053878710358</v>
+        <v>1.687254702195606</v>
       </c>
       <c r="D37">
-        <v>5.978553878710358</v>
+        <v>5.904654702195606</v>
       </c>
       <c r="E37">
-        <v>-2.4335</v>
+        <v>-2.313599999999999</v>
       </c>
       <c r="F37">
-        <v>4.1965</v>
+        <v>4.316400000000001</v>
       </c>
       <c r="G37">
         <v>0.099</v>
@@ -4304,37 +4315,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M37">
-        <v>0.9895347000000001</v>
+        <v>1.01780712</v>
       </c>
       <c r="N37">
-        <v>-1.0885347</v>
+        <v>-1.11680712</v>
       </c>
       <c r="O37">
-        <v>-0.272133675</v>
+        <v>-0.2792017800000001</v>
       </c>
       <c r="P37">
-        <v>-0.816401025</v>
+        <v>-0.8376053400000002</v>
       </c>
       <c r="Q37">
-        <v>-0.2514010250000001</v>
+        <v>-0.2726053400000003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1738748012542315</v>
+        <v>0.1758759700238289</v>
       </c>
       <c r="T37">
-        <v>1.981276442735172</v>
+        <v>2.012233887152909</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.02501175552509677</v>
+        <v>-0.02431698453828852</v>
       </c>
       <c r="W37">
-        <v>0.2416977719528178</v>
+        <v>0.2415339449541284</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4342,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.1000470221003871</v>
+        <v>-0.09726793815315427</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4350,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1995128409987367</v>
+        <v>0.2014128409987367</v>
       </c>
       <c r="C38">
-        <v>1.687254702195607</v>
+        <v>1.495260112429312</v>
       </c>
       <c r="D38">
-        <v>5.904654702195606</v>
+        <v>5.832560112429312</v>
       </c>
       <c r="E38">
-        <v>-2.3136</v>
+        <v>-2.1937</v>
       </c>
       <c r="F38">
-        <v>4.3164</v>
+        <v>4.4363</v>
       </c>
       <c r="G38">
         <v>0.099</v>
@@ -4386,37 +4397,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M38">
-        <v>1.01780712</v>
+        <v>1.04607954</v>
       </c>
       <c r="N38">
-        <v>-1.11680712</v>
+        <v>-1.14507954</v>
       </c>
       <c r="O38">
-        <v>-0.27920178</v>
+        <v>-0.286269885</v>
       </c>
       <c r="P38">
-        <v>-0.8376053400000001</v>
+        <v>-0.8588096549999999</v>
       </c>
       <c r="Q38">
-        <v>-0.2726053400000001</v>
+        <v>-0.293809655</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1758759700238289</v>
+        <v>0.177940667960715</v>
       </c>
       <c r="T38">
-        <v>2.012233887152909</v>
+        <v>2.044174107583907</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.02431698453828853</v>
+        <v>-0.02365976873995641</v>
       </c>
       <c r="W38">
-        <v>0.2415339449541284</v>
+        <v>0.2413789734688817</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4424,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.09726793815315427</v>
+        <v>-0.0946390749598256</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4432,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2014128409987367</v>
+        <v>0.2033128409987367</v>
       </c>
       <c r="C39">
-        <v>1.495260112429312</v>
+        <v>1.305004805881925</v>
       </c>
       <c r="D39">
-        <v>5.832560112429312</v>
+        <v>5.762204805881925</v>
       </c>
       <c r="E39">
-        <v>-2.1937</v>
+        <v>-2.073799999999999</v>
       </c>
       <c r="F39">
-        <v>4.4363</v>
+        <v>4.5562</v>
       </c>
       <c r="G39">
         <v>0.099</v>
@@ -4468,37 +4479,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M39">
-        <v>1.04607954</v>
+        <v>1.07435196</v>
       </c>
       <c r="N39">
-        <v>-1.14507954</v>
+        <v>-1.17335196</v>
       </c>
       <c r="O39">
-        <v>-0.286269885</v>
+        <v>-0.29333799</v>
       </c>
       <c r="P39">
-        <v>-0.8588096549999999</v>
+        <v>-0.8800139700000001</v>
       </c>
       <c r="Q39">
-        <v>-0.293809655</v>
+        <v>-0.3150139700000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.177940667960715</v>
+        <v>0.1800719690568556</v>
       </c>
       <c r="T39">
-        <v>2.044174107583907</v>
+        <v>2.077144657706229</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.02365976873995641</v>
+        <v>-0.02303714324679966</v>
       </c>
       <c r="W39">
-        <v>0.2413789734688817</v>
+        <v>0.2412321583775954</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4506,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.0946390749598256</v>
+        <v>-0.0921485729871987</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4514,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2033128409987367</v>
+        <v>0.2052128409987367</v>
       </c>
       <c r="C40">
-        <v>1.305004805881925</v>
+        <v>1.116426592366727</v>
       </c>
       <c r="D40">
-        <v>5.762204805881925</v>
+        <v>5.693526592366727</v>
       </c>
       <c r="E40">
-        <v>-2.073799999999999</v>
+        <v>-1.9539</v>
       </c>
       <c r="F40">
-        <v>4.5562</v>
+        <v>4.6761</v>
       </c>
       <c r="G40">
         <v>0.099</v>
@@ -4550,37 +4561,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M40">
-        <v>1.07435196</v>
+        <v>1.10262438</v>
       </c>
       <c r="N40">
-        <v>-1.17335196</v>
+        <v>-1.20162438</v>
       </c>
       <c r="O40">
-        <v>-0.29333799</v>
+        <v>-0.300406095</v>
       </c>
       <c r="P40">
-        <v>-0.8800139700000001</v>
+        <v>-0.9012182849999999</v>
       </c>
       <c r="Q40">
-        <v>-0.3150139700000002</v>
+        <v>-0.336218285</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1800719690568556</v>
+        <v>0.1822731488774598</v>
       </c>
       <c r="T40">
-        <v>2.077144657706229</v>
+        <v>2.111196209471905</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.02303714324679966</v>
+        <v>-0.02244644726611249</v>
       </c>
       <c r="W40">
-        <v>0.2412321583775954</v>
+        <v>0.2410928722653493</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4588,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.0921485729871987</v>
+        <v>-0.08978578906445001</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4596,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2052128409987367</v>
+        <v>0.2071128409987367</v>
       </c>
       <c r="C41">
-        <v>1.116426592366727</v>
+        <v>0.9294662116895216</v>
       </c>
       <c r="D41">
-        <v>5.693526592366727</v>
+        <v>5.626466211689522</v>
       </c>
       <c r="E41">
-        <v>-1.9539</v>
+        <v>-1.834</v>
       </c>
       <c r="F41">
-        <v>4.6761</v>
+        <v>4.796</v>
       </c>
       <c r="G41">
         <v>0.099</v>
@@ -4632,37 +4643,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M41">
-        <v>1.10262438</v>
+        <v>1.1308968</v>
       </c>
       <c r="N41">
-        <v>-1.20162438</v>
+        <v>-1.2298968</v>
       </c>
       <c r="O41">
-        <v>-0.300406095</v>
+        <v>-0.3074742</v>
       </c>
       <c r="P41">
-        <v>-0.9012182849999999</v>
+        <v>-0.9224226000000001</v>
       </c>
       <c r="Q41">
-        <v>-0.336218285</v>
+        <v>-0.3574226000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1822731488774598</v>
+        <v>0.1845477013587508</v>
       </c>
       <c r="T41">
-        <v>2.111196209471905</v>
+        <v>2.146382812963103</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.02244644726611249</v>
+        <v>-0.02188528608445968</v>
       </c>
       <c r="W41">
-        <v>0.2410928722653493</v>
+        <v>0.2409605504587156</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4670,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.08978578906445001</v>
+        <v>-0.08754114433783866</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4678,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2071128409987367</v>
+        <v>0.2090128409987367</v>
       </c>
       <c r="C42">
-        <v>0.9294662116895216</v>
+        <v>0.7440671631049005</v>
       </c>
       <c r="D42">
-        <v>5.626466211689522</v>
+        <v>5.560967163104901</v>
       </c>
       <c r="E42">
-        <v>-1.834</v>
+        <v>-1.714099999999999</v>
       </c>
       <c r="F42">
-        <v>4.796</v>
+        <v>4.915900000000001</v>
       </c>
       <c r="G42">
         <v>0.099</v>
@@ -4714,37 +4725,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M42">
-        <v>1.1308968</v>
+        <v>1.15916922</v>
       </c>
       <c r="N42">
-        <v>-1.2298968</v>
+        <v>-1.25816922</v>
       </c>
       <c r="O42">
-        <v>-0.3074742</v>
+        <v>-0.314542305</v>
       </c>
       <c r="P42">
-        <v>-0.9224226000000001</v>
+        <v>-0.9436269150000001</v>
       </c>
       <c r="Q42">
-        <v>-0.3574226000000001</v>
+        <v>-0.3786269150000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1845477013587508</v>
+        <v>0.1868993573139839</v>
       </c>
       <c r="T42">
-        <v>2.146382812963103</v>
+        <v>2.182762182674342</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.02188528608445968</v>
+        <v>-0.02135149861898505</v>
       </c>
       <c r="W42">
-        <v>0.2409605504587156</v>
+        <v>0.2408346833743567</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4752,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.08754114433783866</v>
+        <v>-0.08540599447594022</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4760,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2090128409987367</v>
+        <v>0.2109128409987367</v>
       </c>
       <c r="C43">
-        <v>0.7440671631049005</v>
+        <v>0.5601755465474705</v>
       </c>
       <c r="D43">
-        <v>5.560967163104901</v>
+        <v>5.496975546547471</v>
       </c>
       <c r="E43">
-        <v>-1.714099999999999</v>
+        <v>-1.594199999999999</v>
       </c>
       <c r="F43">
-        <v>4.915900000000001</v>
+        <v>5.035800000000001</v>
       </c>
       <c r="G43">
         <v>0.099</v>
@@ -4796,37 +4807,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M43">
-        <v>1.15916922</v>
+        <v>1.18744164</v>
       </c>
       <c r="N43">
-        <v>-1.25816922</v>
+        <v>-1.28644164</v>
       </c>
       <c r="O43">
-        <v>-0.314542305</v>
+        <v>-0.3216104100000001</v>
       </c>
       <c r="P43">
-        <v>-0.9436269150000001</v>
+        <v>-0.9648312300000002</v>
       </c>
       <c r="Q43">
-        <v>-0.3786269150000001</v>
+        <v>-0.3998312300000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1868993573139839</v>
+        <v>0.1893321048538801</v>
       </c>
       <c r="T43">
-        <v>2.182762182674342</v>
+        <v>2.220396013410106</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.02135149861898505</v>
+        <v>-0.02084312960424731</v>
       </c>
       <c r="W43">
-        <v>0.2408346833743567</v>
+        <v>0.2407148099606815</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4834,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.08540599447594022</v>
+        <v>-0.08337251841698934</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4842,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2109128409987367</v>
+        <v>0.2128128409987367</v>
       </c>
       <c r="C44">
-        <v>0.5601755465474705</v>
+        <v>0.3777399147003413</v>
       </c>
       <c r="D44">
-        <v>5.49697554654747</v>
+        <v>5.434439914700341</v>
       </c>
       <c r="E44">
-        <v>-1.5942</v>
+        <v>-1.474299999999999</v>
       </c>
       <c r="F44">
-        <v>5.0358</v>
+        <v>5.1557</v>
       </c>
       <c r="G44">
         <v>0.099</v>
@@ -4878,37 +4889,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M44">
-        <v>1.18744164</v>
+        <v>1.21571406</v>
       </c>
       <c r="N44">
-        <v>-1.28644164</v>
+        <v>-1.31471406</v>
       </c>
       <c r="O44">
-        <v>-0.32161041</v>
+        <v>-0.328678515</v>
       </c>
       <c r="P44">
-        <v>-0.96483123</v>
+        <v>-0.986035545</v>
       </c>
       <c r="Q44">
-        <v>-0.3998312300000001</v>
+        <v>-0.4210355450000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1893321048538801</v>
+        <v>0.1918502119565798</v>
       </c>
       <c r="T44">
-        <v>2.220396013410106</v>
+        <v>2.259350329434845</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.02084312960424731</v>
+        <v>-0.02035840565996249</v>
       </c>
       <c r="W44">
-        <v>0.2407148099606815</v>
+        <v>0.2406005120546191</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4916,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.08337251841698934</v>
+        <v>-0.08143362263984999</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4924,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2128128409987367</v>
+        <v>0.2147128409987367</v>
       </c>
       <c r="C45">
-        <v>0.3777399147003413</v>
+        <v>0.1967111350475976</v>
       </c>
       <c r="D45">
-        <v>5.434439914700341</v>
+        <v>5.373311135047597</v>
       </c>
       <c r="E45">
-        <v>-1.474299999999999</v>
+        <v>-1.3544</v>
       </c>
       <c r="F45">
-        <v>5.1557</v>
+        <v>5.2756</v>
       </c>
       <c r="G45">
         <v>0.099</v>
@@ -4960,37 +4971,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M45">
-        <v>1.21571406</v>
+        <v>1.24398648</v>
       </c>
       <c r="N45">
-        <v>-1.31471406</v>
+        <v>-1.34298648</v>
       </c>
       <c r="O45">
-        <v>-0.328678515</v>
+        <v>-0.33574662</v>
       </c>
       <c r="P45">
-        <v>-0.986035545</v>
+        <v>-1.00723986</v>
       </c>
       <c r="Q45">
-        <v>-0.4210355450000001</v>
+        <v>-0.4422398599999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1918502119565798</v>
+        <v>0.1944582514558044</v>
       </c>
       <c r="T45">
-        <v>2.259350329434845</v>
+        <v>2.299695871031896</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.02035840565996249</v>
+        <v>-0.01989571462223607</v>
       </c>
       <c r="W45">
-        <v>0.2406005120546191</v>
+        <v>0.2404914095079233</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4998,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.08143362263984999</v>
+        <v>-0.07958285848894442</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5006,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2147128409987367</v>
+        <v>0.2166128409987367</v>
       </c>
       <c r="C46">
-        <v>0.1967111350475976</v>
+        <v>0.01704226113333451</v>
       </c>
       <c r="D46">
-        <v>5.373311135047597</v>
+        <v>5.313542261133334</v>
       </c>
       <c r="E46">
-        <v>-1.3544</v>
+        <v>-1.2345</v>
       </c>
       <c r="F46">
-        <v>5.2756</v>
+        <v>5.3955</v>
       </c>
       <c r="G46">
         <v>0.099</v>
@@ -5042,37 +5053,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M46">
-        <v>1.24398648</v>
+        <v>1.2722589</v>
       </c>
       <c r="N46">
-        <v>-1.34298648</v>
+        <v>-1.3712589</v>
       </c>
       <c r="O46">
-        <v>-0.33574662</v>
+        <v>-0.342814725</v>
       </c>
       <c r="P46">
-        <v>-1.00723986</v>
+        <v>-1.028444175</v>
       </c>
       <c r="Q46">
-        <v>-0.4422398599999999</v>
+        <v>-0.4634441750000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1944582514558044</v>
+        <v>0.1971611287550009</v>
       </c>
       <c r="T46">
-        <v>2.299695871031896</v>
+        <v>2.341508523232476</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.01989571462223607</v>
+        <v>-0.01945358763063082</v>
       </c>
       <c r="W46">
-        <v>0.2404914095079233</v>
+        <v>0.2403871559633027</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5080,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.07958285848894442</v>
+        <v>-0.07781435052252328</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5088,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2166128409987367</v>
+        <v>0.2185128409987367</v>
       </c>
       <c r="C47">
-        <v>0.01704226113333451</v>
+        <v>-0.1613115876816877</v>
       </c>
       <c r="D47">
-        <v>5.313542261133334</v>
+        <v>5.255088412318313</v>
       </c>
       <c r="E47">
-        <v>-1.2345</v>
+        <v>-1.114599999999999</v>
       </c>
       <c r="F47">
-        <v>5.3955</v>
+        <v>5.515400000000001</v>
       </c>
       <c r="G47">
         <v>0.099</v>
@@ -5124,37 +5135,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M47">
-        <v>1.2722589</v>
+        <v>1.30053132</v>
       </c>
       <c r="N47">
-        <v>-1.3712589</v>
+        <v>-1.39953132</v>
       </c>
       <c r="O47">
-        <v>-0.342814725</v>
+        <v>-0.34988283</v>
       </c>
       <c r="P47">
-        <v>-1.028444175</v>
+        <v>-1.04964849</v>
       </c>
       <c r="Q47">
-        <v>-0.4634441750000002</v>
+        <v>-0.4846484900000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1971611287550009</v>
+        <v>0.1999641126208342</v>
       </c>
       <c r="T47">
-        <v>2.341508523232476</v>
+        <v>2.384869792181225</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.01945358763063082</v>
+        <v>-0.01903068355170407</v>
       </c>
       <c r="W47">
-        <v>0.2403871559633027</v>
+        <v>0.2402874351814918</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5162,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.07781435052252328</v>
+        <v>-0.07612273420681626</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5170,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2185128409987367</v>
+        <v>0.2204128409987367</v>
       </c>
       <c r="C48">
-        <v>-0.1613115876816877</v>
+        <v>-0.3383933386130371</v>
       </c>
       <c r="D48">
-        <v>5.255088412318313</v>
+        <v>5.197906661386964</v>
       </c>
       <c r="E48">
-        <v>-1.114599999999999</v>
+        <v>-0.994699999999999</v>
       </c>
       <c r="F48">
-        <v>5.515400000000001</v>
+        <v>5.635300000000001</v>
       </c>
       <c r="G48">
         <v>0.099</v>
@@ -5206,37 +5217,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M48">
-        <v>1.30053132</v>
+        <v>1.32880374</v>
       </c>
       <c r="N48">
-        <v>-1.39953132</v>
+        <v>-1.42780374</v>
       </c>
       <c r="O48">
-        <v>-0.34988283</v>
+        <v>-0.3569509350000001</v>
       </c>
       <c r="P48">
-        <v>-1.04964849</v>
+        <v>-1.070852805</v>
       </c>
       <c r="Q48">
-        <v>-0.4846484900000001</v>
+        <v>-0.5058528050000004</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1999641126208342</v>
+        <v>0.2028728694627367</v>
       </c>
       <c r="T48">
-        <v>2.384869792181225</v>
+        <v>2.429867335429928</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.01903068355170407</v>
+        <v>-0.01862577539102951</v>
       </c>
       <c r="W48">
-        <v>0.2402874351814918</v>
+        <v>0.2401919578372048</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5244,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.07612273420681626</v>
+        <v>-0.07450310156411799</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5252,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2204128409987367</v>
+        <v>0.2223128409987367</v>
       </c>
       <c r="C49">
-        <v>-0.3383933386130371</v>
+        <v>-0.5142440705867291</v>
       </c>
       <c r="D49">
-        <v>5.197906661386964</v>
+        <v>5.141955929413271</v>
       </c>
       <c r="E49">
-        <v>-0.994699999999999</v>
+        <v>-0.8747999999999996</v>
       </c>
       <c r="F49">
-        <v>5.635300000000001</v>
+        <v>5.7552</v>
       </c>
       <c r="G49">
         <v>0.099</v>
@@ -5288,37 +5299,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M49">
-        <v>1.32880374</v>
+        <v>1.35707616</v>
       </c>
       <c r="N49">
-        <v>-1.42780374</v>
+        <v>-1.45607616</v>
       </c>
       <c r="O49">
-        <v>-0.3569509350000001</v>
+        <v>-0.36401904</v>
       </c>
       <c r="P49">
-        <v>-1.070852805</v>
+        <v>-1.09205712</v>
       </c>
       <c r="Q49">
-        <v>-0.5058528050000004</v>
+        <v>-0.52705712</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2028728694627367</v>
+        <v>0.2058935015677894</v>
       </c>
       <c r="T49">
-        <v>2.429867335429928</v>
+        <v>2.476595553418965</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.01862577539102951</v>
+        <v>-0.0182377384037164</v>
       </c>
       <c r="W49">
-        <v>0.2401919578372048</v>
+        <v>0.2401004587155963</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5326,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.07450310156411799</v>
+        <v>-0.07295095361486559</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5334,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2223128409987367</v>
+        <v>0.2242128409987367</v>
       </c>
       <c r="C50">
-        <v>-0.5142440705867291</v>
+        <v>-0.6889031126556473</v>
       </c>
       <c r="D50">
-        <v>5.141955929413271</v>
+        <v>5.087196887344352</v>
       </c>
       <c r="E50">
-        <v>-0.8747999999999996</v>
+        <v>-0.7549000000000001</v>
       </c>
       <c r="F50">
-        <v>5.7552</v>
+        <v>5.8751</v>
       </c>
       <c r="G50">
         <v>0.099</v>
@@ -5370,37 +5381,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M50">
-        <v>1.35707616</v>
+        <v>1.38534858</v>
       </c>
       <c r="N50">
-        <v>-1.45607616</v>
+        <v>-1.48434858</v>
       </c>
       <c r="O50">
-        <v>-0.36401904</v>
+        <v>-0.371087145</v>
       </c>
       <c r="P50">
-        <v>-1.09205712</v>
+        <v>-1.113261435</v>
       </c>
       <c r="Q50">
-        <v>-0.52705712</v>
+        <v>-0.5482614350000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2058935015677893</v>
+        <v>0.2090325898338245</v>
       </c>
       <c r="T50">
-        <v>2.476595553418965</v>
+        <v>2.525156250544827</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.0182377384037164</v>
+        <v>-0.01786553966078341</v>
       </c>
       <c r="W50">
-        <v>0.2401004587155963</v>
+        <v>0.2400126942520127</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5408,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.07295095361486559</v>
+        <v>-0.07146215864313366</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5416,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2242128409987367</v>
+        <v>0.2261128409987367</v>
       </c>
       <c r="C51">
-        <v>-0.6889031126556473</v>
+        <v>-0.8624081361937206</v>
       </c>
       <c r="D51">
-        <v>5.087196887344352</v>
+        <v>5.033591863806279</v>
       </c>
       <c r="E51">
-        <v>-0.7549000000000001</v>
+        <v>-0.6349999999999998</v>
       </c>
       <c r="F51">
-        <v>5.8751</v>
+        <v>5.995</v>
       </c>
       <c r="G51">
         <v>0.099</v>
@@ -5452,37 +5463,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M51">
-        <v>1.38534858</v>
+        <v>1.413621</v>
       </c>
       <c r="N51">
-        <v>-1.48434858</v>
+        <v>-1.512621</v>
       </c>
       <c r="O51">
-        <v>-0.371087145</v>
+        <v>-0.37815525</v>
       </c>
       <c r="P51">
-        <v>-1.113261435</v>
+        <v>-1.13446575</v>
       </c>
       <c r="Q51">
-        <v>-0.5482614350000001</v>
+        <v>-0.56946575</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2090325898338245</v>
+        <v>0.212297241630501</v>
       </c>
       <c r="T51">
-        <v>2.525156250544827</v>
+        <v>2.575659375555724</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.01786553966078341</v>
+        <v>-0.01750822886756774</v>
       </c>
       <c r="W51">
-        <v>0.2400126942520127</v>
+        <v>0.2399284403669725</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5490,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.07146215864313366</v>
+        <v>-0.07003291547027102</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5498,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2261128409987367</v>
+        <v>0.2280128409987367</v>
       </c>
       <c r="C52">
-        <v>-0.8624081361937206</v>
+        <v>-1.034795241322049</v>
       </c>
       <c r="D52">
-        <v>5.033591863806279</v>
+        <v>4.981104758677951</v>
       </c>
       <c r="E52">
-        <v>-0.6349999999999998</v>
+        <v>-0.5150999999999994</v>
       </c>
       <c r="F52">
-        <v>5.995</v>
+        <v>6.1149</v>
       </c>
       <c r="G52">
         <v>0.099</v>
@@ -5534,37 +5545,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M52">
-        <v>1.413621</v>
+        <v>1.44189342</v>
       </c>
       <c r="N52">
-        <v>-1.512621</v>
+        <v>-1.54089342</v>
       </c>
       <c r="O52">
-        <v>-0.37815525</v>
+        <v>-0.385223355</v>
       </c>
       <c r="P52">
-        <v>-1.13446575</v>
+        <v>-1.155670065</v>
       </c>
       <c r="Q52">
-        <v>-0.56946575</v>
+        <v>-0.5906700650000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.212297241630501</v>
+        <v>0.2156951445209193</v>
       </c>
       <c r="T52">
-        <v>2.575659375555724</v>
+        <v>2.628223852607881</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.01750822886756774</v>
+        <v>-0.01716493026232132</v>
       </c>
       <c r="W52">
-        <v>0.2399284403669725</v>
+        <v>0.2398474905558554</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5572,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.07003291547027102</v>
+        <v>-0.06865972104928519</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5580,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2280128409987367</v>
+        <v>0.2299128409987368</v>
       </c>
       <c r="C53">
-        <v>-1.034795241322049</v>
+        <v>-1.206099037983648</v>
       </c>
       <c r="D53">
-        <v>4.981104758677951</v>
+        <v>4.929700962016351</v>
       </c>
       <c r="E53">
-        <v>-0.5150999999999994</v>
+        <v>-0.3952</v>
       </c>
       <c r="F53">
-        <v>6.1149</v>
+        <v>6.2348</v>
       </c>
       <c r="G53">
         <v>0.099</v>
@@ -5616,37 +5627,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M53">
-        <v>1.44189342</v>
+        <v>1.47016584</v>
       </c>
       <c r="N53">
-        <v>-1.54089342</v>
+        <v>-1.56916584</v>
       </c>
       <c r="O53">
-        <v>-0.385223355</v>
+        <v>-0.39229146</v>
       </c>
       <c r="P53">
-        <v>-1.155670065</v>
+        <v>-1.17687438</v>
       </c>
       <c r="Q53">
-        <v>-0.5906700650000003</v>
+        <v>-0.6118743799999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2156951445209193</v>
+        <v>0.2192346266984385</v>
       </c>
       <c r="T53">
-        <v>2.628223852607881</v>
+        <v>2.682978516203879</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.01716493026232132</v>
+        <v>-0.01683483544958437</v>
       </c>
       <c r="W53">
-        <v>0.2398474905558554</v>
+        <v>0.239769654199012</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5654,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.06865972104928519</v>
+        <v>-0.06733934179833745</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5662,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2299128409987368</v>
+        <v>0.2318128409987367</v>
       </c>
       <c r="C54">
-        <v>-1.206099037983648</v>
+        <v>-1.37635272204944</v>
       </c>
       <c r="D54">
-        <v>4.929700962016351</v>
+        <v>4.87934727795056</v>
       </c>
       <c r="E54">
-        <v>-0.3952</v>
+        <v>-0.2752999999999997</v>
       </c>
       <c r="F54">
-        <v>6.2348</v>
+        <v>6.3547</v>
       </c>
       <c r="G54">
         <v>0.099</v>
@@ -5698,37 +5709,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M54">
-        <v>1.47016584</v>
+        <v>1.49843826</v>
       </c>
       <c r="N54">
-        <v>-1.56916584</v>
+        <v>-1.59743826</v>
       </c>
       <c r="O54">
-        <v>-0.39229146</v>
+        <v>-0.399359565</v>
       </c>
       <c r="P54">
-        <v>-1.17687438</v>
+        <v>-1.198078695</v>
       </c>
       <c r="Q54">
-        <v>-0.6118743799999999</v>
+        <v>-0.633078695</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2192346266984385</v>
+        <v>0.2229247251388308</v>
       </c>
       <c r="T54">
-        <v>2.682978516203879</v>
+        <v>2.740063165484813</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.01683483544958437</v>
+        <v>-0.01651719704487523</v>
       </c>
       <c r="W54">
-        <v>0.239769654199012</v>
+        <v>0.2396947550631816</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5736,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.06733934179833745</v>
+        <v>-0.06606878817950101</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5744,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2318128409987367</v>
+        <v>0.2337128409987367</v>
       </c>
       <c r="C55">
-        <v>-1.37635272204944</v>
+        <v>-1.545588146807179</v>
       </c>
       <c r="D55">
-        <v>4.87934727795056</v>
+        <v>4.830011853192821</v>
       </c>
       <c r="E55">
-        <v>-0.2752999999999997</v>
+        <v>-0.1553999999999993</v>
       </c>
       <c r="F55">
-        <v>6.3547</v>
+        <v>6.474600000000001</v>
       </c>
       <c r="G55">
         <v>0.099</v>
@@ -5780,37 +5791,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M55">
-        <v>1.49843826</v>
+        <v>1.52671068</v>
       </c>
       <c r="N55">
-        <v>-1.59743826</v>
+        <v>-1.62571068</v>
       </c>
       <c r="O55">
-        <v>-0.399359565</v>
+        <v>-0.40642767</v>
       </c>
       <c r="P55">
-        <v>-1.198078695</v>
+        <v>-1.21928301</v>
       </c>
       <c r="Q55">
-        <v>-0.633078695</v>
+        <v>-0.6542830100000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2229247251388308</v>
+        <v>0.2267752626418488</v>
       </c>
       <c r="T55">
-        <v>2.740063165484813</v>
+        <v>2.79962975603883</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.01651719704487523</v>
+        <v>-0.01621132302552569</v>
       </c>
       <c r="W55">
-        <v>0.2396947550631816</v>
+        <v>0.239622629969419</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5818,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.06606878817950101</v>
+        <v>-0.06484529210210277</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5826,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2337128409987367</v>
+        <v>0.2356128409987368</v>
       </c>
       <c r="C56">
-        <v>-1.545588146807179</v>
+        <v>-1.713835890156786</v>
       </c>
       <c r="D56">
-        <v>4.830011853192821</v>
+        <v>4.781664109843215</v>
       </c>
       <c r="E56">
-        <v>-0.1553999999999993</v>
+        <v>-0.03549999999999898</v>
       </c>
       <c r="F56">
-        <v>6.474600000000001</v>
+        <v>6.594500000000001</v>
       </c>
       <c r="G56">
         <v>0.099</v>
@@ -5862,37 +5873,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M56">
-        <v>1.52671068</v>
+        <v>1.5549831</v>
       </c>
       <c r="N56">
-        <v>-1.62571068</v>
+        <v>-1.6539831</v>
       </c>
       <c r="O56">
-        <v>-0.40642767</v>
+        <v>-0.4134957750000001</v>
       </c>
       <c r="P56">
-        <v>-1.21928301</v>
+        <v>-1.240487325</v>
       </c>
       <c r="Q56">
-        <v>-0.6542830100000001</v>
+        <v>-0.6754873250000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2267752626418488</v>
+        <v>0.2307969351450011</v>
       </c>
       <c r="T56">
-        <v>2.79962975603883</v>
+        <v>2.861843750617471</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.01621132302552569</v>
+        <v>-0.01591657169778886</v>
       </c>
       <c r="W56">
-        <v>0.239622629969419</v>
+        <v>0.2395531276063387</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5900,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.06484529210210277</v>
+        <v>-0.06366628679115549</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5908,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2356128409987368</v>
+        <v>0.2375128409987367</v>
       </c>
       <c r="C57">
-        <v>-1.713835890156786</v>
+        <v>-1.88112531781</v>
       </c>
       <c r="D57">
-        <v>4.781664109843215</v>
+        <v>4.734274682190001</v>
       </c>
       <c r="E57">
-        <v>-0.03549999999999898</v>
+        <v>0.08440000000000047</v>
       </c>
       <c r="F57">
-        <v>6.594500000000001</v>
+        <v>6.7144</v>
       </c>
       <c r="G57">
         <v>0.099</v>
@@ -5944,37 +5955,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M57">
-        <v>1.5549831</v>
+        <v>1.58325552</v>
       </c>
       <c r="N57">
-        <v>-1.6539831</v>
+        <v>-1.68225552</v>
       </c>
       <c r="O57">
-        <v>-0.4134957750000001</v>
+        <v>-0.4205638800000001</v>
       </c>
       <c r="P57">
-        <v>-1.240487325</v>
+        <v>-1.26169164</v>
       </c>
       <c r="Q57">
-        <v>-0.6754873250000002</v>
+        <v>-0.6966916400000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2307969351450011</v>
+        <v>0.2350014109437511</v>
       </c>
       <c r="T57">
-        <v>2.861843750617471</v>
+        <v>2.926885654040595</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.01591657169778886</v>
+        <v>-0.01563234720318548</v>
       </c>
       <c r="W57">
-        <v>0.2395531276063387</v>
+        <v>0.2394861074705111</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5982,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.06366628679115549</v>
+        <v>-0.06252938881274206</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5990,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2375128409987367</v>
+        <v>0.2394128409987367</v>
       </c>
       <c r="C58">
-        <v>-1.88112531781</v>
+        <v>-2.047484642768823</v>
       </c>
       <c r="D58">
-        <v>4.734274682190001</v>
+        <v>4.687815357231178</v>
       </c>
       <c r="E58">
-        <v>0.08440000000000047</v>
+        <v>0.2043000000000008</v>
       </c>
       <c r="F58">
-        <v>6.7144</v>
+        <v>6.834300000000001</v>
       </c>
       <c r="G58">
         <v>0.099</v>
@@ -6026,37 +6037,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M58">
-        <v>1.58325552</v>
+        <v>1.61152794</v>
       </c>
       <c r="N58">
-        <v>-1.68225552</v>
+        <v>-1.71052794</v>
       </c>
       <c r="O58">
-        <v>-0.4205638800000001</v>
+        <v>-0.427631985</v>
       </c>
       <c r="P58">
-        <v>-1.26169164</v>
+        <v>-1.282895955</v>
       </c>
       <c r="Q58">
-        <v>-0.6966916400000003</v>
+        <v>-0.7178959550000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2350014109437511</v>
+        <v>0.2394014437563965</v>
       </c>
       <c r="T58">
-        <v>2.926885654040595</v>
+        <v>2.994952762274098</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.01563234720318548</v>
+        <v>-0.01535809549786644</v>
       </c>
       <c r="W58">
-        <v>0.2394861074705111</v>
+        <v>0.2394214389183969</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6064,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.06252938881274206</v>
+        <v>-0.06143238199146572</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6072,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2394128409987367</v>
+        <v>0.2413128409987367</v>
       </c>
       <c r="C59">
-        <v>-2.047484642768823</v>
+        <v>-2.212940981335847</v>
       </c>
       <c r="D59">
-        <v>4.687815357231178</v>
+        <v>4.642259018664154</v>
       </c>
       <c r="E59">
-        <v>0.2043000000000008</v>
+        <v>0.3242000000000012</v>
       </c>
       <c r="F59">
-        <v>6.834300000000001</v>
+        <v>6.954200000000001</v>
       </c>
       <c r="G59">
         <v>0.099</v>
@@ -6108,37 +6119,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M59">
-        <v>1.61152794</v>
+        <v>1.63980036</v>
       </c>
       <c r="N59">
-        <v>-1.71052794</v>
+        <v>-1.73880036</v>
       </c>
       <c r="O59">
-        <v>-0.427631985</v>
+        <v>-0.4347000900000001</v>
       </c>
       <c r="P59">
-        <v>-1.282895955</v>
+        <v>-1.30410027</v>
       </c>
       <c r="Q59">
-        <v>-0.7178959550000001</v>
+        <v>-0.7391002700000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2394014437563965</v>
+        <v>0.2440110019410726</v>
       </c>
       <c r="T59">
-        <v>2.994952762274098</v>
+        <v>3.066261161375862</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.01535809549786644</v>
+        <v>-0.01509330074790322</v>
       </c>
       <c r="W59">
-        <v>0.2394214389183969</v>
+        <v>0.2393590003163556</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6146,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.06143238199146572</v>
+        <v>-0.06037320299161286</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6154,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2413128409987367</v>
+        <v>0.2432128409987367</v>
       </c>
       <c r="C60">
-        <v>-2.212940981335844</v>
+        <v>-2.37752040589019</v>
       </c>
       <c r="D60">
-        <v>4.642259018664155</v>
+        <v>4.59757959410981</v>
       </c>
       <c r="E60">
-        <v>0.3241999999999994</v>
+        <v>0.4440999999999997</v>
       </c>
       <c r="F60">
-        <v>6.954199999999999</v>
+        <v>7.0741</v>
       </c>
       <c r="G60">
         <v>0.099</v>
@@ -6190,37 +6201,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M60">
-        <v>1.63980036</v>
+        <v>1.66807278</v>
       </c>
       <c r="N60">
-        <v>-1.73880036</v>
+        <v>-1.76707278</v>
       </c>
       <c r="O60">
-        <v>-0.43470009</v>
+        <v>-0.441768195</v>
       </c>
       <c r="P60">
-        <v>-1.30410027</v>
+        <v>-1.325304585</v>
       </c>
       <c r="Q60">
-        <v>-0.73910027</v>
+        <v>-0.7603045850000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2440110019410725</v>
+        <v>0.2488454166225621</v>
       </c>
       <c r="T60">
-        <v>3.066261161375861</v>
+        <v>3.141048018970394</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.01509330074790323</v>
+        <v>-0.01483748209115911</v>
       </c>
       <c r="W60">
-        <v>0.2393590003163556</v>
+        <v>0.2392986782770954</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6228,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.06037320299161286</v>
+        <v>-0.05934992836463637</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6236,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2432128409987367</v>
+        <v>0.2451128409987367</v>
       </c>
       <c r="C61">
-        <v>-2.37752040589019</v>
+        <v>-2.541247994644815</v>
       </c>
       <c r="D61">
-        <v>4.59757959410981</v>
+        <v>4.553752005355185</v>
       </c>
       <c r="E61">
-        <v>0.4440999999999997</v>
+        <v>0.5640000000000001</v>
       </c>
       <c r="F61">
-        <v>7.0741</v>
+        <v>7.194</v>
       </c>
       <c r="G61">
         <v>0.099</v>
@@ -6272,37 +6283,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M61">
-        <v>1.66807278</v>
+        <v>1.6963452</v>
       </c>
       <c r="N61">
-        <v>-1.76707278</v>
+        <v>-1.7953452</v>
       </c>
       <c r="O61">
-        <v>-0.441768195</v>
+        <v>-0.4488363</v>
       </c>
       <c r="P61">
-        <v>-1.325304585</v>
+        <v>-1.3465089</v>
       </c>
       <c r="Q61">
-        <v>-0.7603045850000001</v>
+        <v>-0.7815089000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2488454166225621</v>
+        <v>0.2539215520381262</v>
       </c>
       <c r="T61">
-        <v>3.141048018970394</v>
+        <v>3.219574219444654</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.01483748209115911</v>
+        <v>-0.01459019072297312</v>
       </c>
       <c r="W61">
-        <v>0.2392986782770954</v>
+        <v>0.2392403669724771</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6310,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.05934992836463637</v>
+        <v>-0.05836076289189251</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6318,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2451128409987367</v>
+        <v>0.2470128409987367</v>
       </c>
       <c r="C62">
-        <v>-2.541247994644815</v>
+        <v>-2.704147878584774</v>
       </c>
       <c r="D62">
-        <v>4.553752005355185</v>
+        <v>4.510752121415226</v>
       </c>
       <c r="E62">
-        <v>0.5640000000000001</v>
+        <v>0.6839000000000004</v>
       </c>
       <c r="F62">
-        <v>7.194</v>
+        <v>7.3139</v>
       </c>
       <c r="G62">
         <v>0.099</v>
@@ -6354,37 +6365,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M62">
-        <v>1.6963452</v>
+        <v>1.72461762</v>
       </c>
       <c r="N62">
-        <v>-1.7953452</v>
+        <v>-1.82361762</v>
       </c>
       <c r="O62">
-        <v>-0.4488363</v>
+        <v>-0.455904405</v>
       </c>
       <c r="P62">
-        <v>-1.3465089</v>
+        <v>-1.367713215</v>
       </c>
       <c r="Q62">
-        <v>-0.7815089000000002</v>
+        <v>-0.802713215</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2539215520381262</v>
+        <v>0.2592580020903858</v>
       </c>
       <c r="T62">
-        <v>3.219574219444654</v>
+        <v>3.30212740455862</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.01459019072297312</v>
+        <v>-0.01435100726849815</v>
       </c>
       <c r="W62">
-        <v>0.2392403669724771</v>
+        <v>0.2391839675139119</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6392,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.05836076289189251</v>
+        <v>-0.05740402907399256</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6400,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2470128409987367</v>
+        <v>0.2489128409987367</v>
       </c>
       <c r="C63">
-        <v>-2.704147878584774</v>
+        <v>-2.866243285770978</v>
       </c>
       <c r="D63">
-        <v>4.510752121415226</v>
+        <v>4.468556714229021</v>
       </c>
       <c r="E63">
-        <v>0.6839000000000004</v>
+        <v>0.8037999999999998</v>
       </c>
       <c r="F63">
-        <v>7.3139</v>
+        <v>7.4338</v>
       </c>
       <c r="G63">
         <v>0.099</v>
@@ -6436,37 +6447,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M63">
-        <v>1.72461762</v>
+        <v>1.75289004</v>
       </c>
       <c r="N63">
-        <v>-1.82361762</v>
+        <v>-1.85189004</v>
       </c>
       <c r="O63">
-        <v>-0.455904405</v>
+        <v>-0.46297251</v>
       </c>
       <c r="P63">
-        <v>-1.367713215</v>
+        <v>-1.38891753</v>
       </c>
       <c r="Q63">
-        <v>-0.802713215</v>
+        <v>-0.8239175300000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2592580020903858</v>
+        <v>0.2648753179348696</v>
       </c>
       <c r="T63">
-        <v>3.30212740455862</v>
+        <v>3.389025494152268</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.01435100726849815</v>
+        <v>-0.01411953940932882</v>
       </c>
       <c r="W63">
-        <v>0.2391839675139119</v>
+        <v>0.2391293873927197</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6474,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.05740402907399256</v>
+        <v>-0.05647815763731523</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6482,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2489128409987367</v>
+        <v>0.2508128409987367</v>
       </c>
       <c r="C64">
-        <v>-2.866243285770978</v>
+        <v>-3.02755658318042</v>
       </c>
       <c r="D64">
-        <v>4.468556714229021</v>
+        <v>4.42714341681958</v>
       </c>
       <c r="E64">
-        <v>0.8037999999999998</v>
+        <v>0.9237000000000002</v>
       </c>
       <c r="F64">
-        <v>7.4338</v>
+        <v>7.5537</v>
       </c>
       <c r="G64">
         <v>0.099</v>
@@ -6518,37 +6529,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M64">
-        <v>1.75289004</v>
+        <v>1.78116246</v>
       </c>
       <c r="N64">
-        <v>-1.85189004</v>
+        <v>-1.88016246</v>
       </c>
       <c r="O64">
-        <v>-0.46297251</v>
+        <v>-0.470040615</v>
       </c>
       <c r="P64">
-        <v>-1.38891753</v>
+        <v>-1.410121845</v>
       </c>
       <c r="Q64">
-        <v>-0.8239175300000001</v>
+        <v>-0.845121845</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2648753179348696</v>
+        <v>0.2707962724736499</v>
       </c>
       <c r="T64">
-        <v>3.389025494152268</v>
+        <v>3.480620777778005</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.01411953940932882</v>
+        <v>-0.01389541973616487</v>
       </c>
       <c r="W64">
-        <v>0.2391293873927197</v>
+        <v>0.2390765399737877</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6556,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.05647815763731523</v>
+        <v>-0.05558167894465948</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6564,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2508128409987367</v>
+        <v>0.2527128409987367</v>
       </c>
       <c r="C65">
-        <v>-3.02755658318042</v>
+        <v>-3.188109316241142</v>
       </c>
       <c r="D65">
-        <v>4.42714341681958</v>
+        <v>4.386490683758858</v>
       </c>
       <c r="E65">
-        <v>0.9237000000000002</v>
+        <v>1.043600000000001</v>
       </c>
       <c r="F65">
-        <v>7.5537</v>
+        <v>7.6736</v>
       </c>
       <c r="G65">
         <v>0.099</v>
@@ -6600,37 +6611,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M65">
-        <v>1.78116246</v>
+        <v>1.80943488</v>
       </c>
       <c r="N65">
-        <v>-1.88016246</v>
+        <v>-1.90843488</v>
       </c>
       <c r="O65">
-        <v>-0.470040615</v>
+        <v>-0.47710872</v>
       </c>
       <c r="P65">
-        <v>-1.410121845</v>
+        <v>-1.43132616</v>
       </c>
       <c r="Q65">
-        <v>-0.845121845</v>
+        <v>-0.8663261600000003</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2707962724736499</v>
+        <v>0.2770461689312513</v>
       </c>
       <c r="T65">
-        <v>3.480620777778005</v>
+        <v>3.577304688271838</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.01389541973616487</v>
+        <v>-0.0136783038027873</v>
       </c>
       <c r="W65">
-        <v>0.2390765399737877</v>
+        <v>0.2390253440366972</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6638,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.05558167894465948</v>
+        <v>-0.05471321521114914</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6646,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2527128409987367</v>
+        <v>0.2546128409987367</v>
       </c>
       <c r="C66">
-        <v>-3.188109316241142</v>
+        <v>-3.347922246208857</v>
       </c>
       <c r="D66">
-        <v>4.386490683758858</v>
+        <v>4.346577753791143</v>
       </c>
       <c r="E66">
-        <v>1.043600000000001</v>
+        <v>1.163500000000001</v>
       </c>
       <c r="F66">
-        <v>7.6736</v>
+        <v>7.793500000000001</v>
       </c>
       <c r="G66">
         <v>0.099</v>
@@ -6682,37 +6693,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M66">
-        <v>1.80943488</v>
+        <v>1.8377073</v>
       </c>
       <c r="N66">
-        <v>-1.90843488</v>
+        <v>-1.9367073</v>
       </c>
       <c r="O66">
-        <v>-0.47710872</v>
+        <v>-0.484176825</v>
       </c>
       <c r="P66">
-        <v>-1.43132616</v>
+        <v>-1.452530475</v>
       </c>
       <c r="Q66">
-        <v>-0.8663261600000003</v>
+        <v>-0.8875304750000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2770461689312513</v>
+        <v>0.283653202329287</v>
       </c>
       <c r="T66">
-        <v>3.577304688271838</v>
+        <v>3.679513393651034</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.0136783038027873</v>
+        <v>-0.01346786835966749</v>
       </c>
       <c r="W66">
-        <v>0.2390253440366972</v>
+        <v>0.2389757233592096</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6720,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.05471321521114914</v>
+        <v>-0.05387147343867005</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6728,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2546128409987367</v>
+        <v>0.2565128409987368</v>
       </c>
       <c r="C67">
-        <v>-3.347922246208857</v>
+        <v>-3.507015385521391</v>
       </c>
       <c r="D67">
-        <v>4.346577753791143</v>
+        <v>4.307384614478609</v>
       </c>
       <c r="E67">
-        <v>1.163500000000001</v>
+        <v>1.2834</v>
       </c>
       <c r="F67">
-        <v>7.793500000000001</v>
+        <v>7.9134</v>
       </c>
       <c r="G67">
         <v>0.099</v>
@@ -6764,37 +6775,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M67">
-        <v>1.8377073</v>
+        <v>1.86597972</v>
       </c>
       <c r="N67">
-        <v>-1.9367073</v>
+        <v>-1.96497972</v>
       </c>
       <c r="O67">
-        <v>-0.484176825</v>
+        <v>-0.49124493</v>
       </c>
       <c r="P67">
-        <v>-1.452530475</v>
+        <v>-1.47373479</v>
       </c>
       <c r="Q67">
-        <v>-0.8875304750000002</v>
+        <v>-0.90873479</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.283653202329287</v>
+        <v>0.2906488847507367</v>
       </c>
       <c r="T67">
-        <v>3.679513393651034</v>
+        <v>3.787734375817241</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.01346786835966749</v>
+        <v>-0.01326380974815738</v>
       </c>
       <c r="W67">
-        <v>0.2389757233592096</v>
+        <v>0.2389276063386155</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6802,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.05387147343867005</v>
+        <v>-0.05305523899262954</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6810,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2565128409987368</v>
+        <v>0.2584128409987367</v>
       </c>
       <c r="C68">
-        <v>-3.507015385521391</v>
+        <v>-3.665408031257487</v>
       </c>
       <c r="D68">
-        <v>4.307384614478609</v>
+        <v>4.268891968742514</v>
       </c>
       <c r="E68">
-        <v>1.2834</v>
+        <v>1.403300000000001</v>
       </c>
       <c r="F68">
-        <v>7.9134</v>
+        <v>8.033300000000001</v>
       </c>
       <c r="G68">
         <v>0.099</v>
@@ -6846,37 +6857,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M68">
-        <v>1.86597972</v>
+        <v>1.89425214</v>
       </c>
       <c r="N68">
-        <v>-1.96497972</v>
+        <v>-1.99325214</v>
       </c>
       <c r="O68">
-        <v>-0.49124493</v>
+        <v>-0.4983130350000001</v>
       </c>
       <c r="P68">
-        <v>-1.47373479</v>
+        <v>-1.494939105</v>
       </c>
       <c r="Q68">
-        <v>-0.90873479</v>
+        <v>-0.9299391050000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2906488847507367</v>
+        <v>0.2980685479250014</v>
       </c>
       <c r="T68">
-        <v>3.787734375817241</v>
+        <v>3.90251420538746</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.01326380974815738</v>
+        <v>-0.01306584243848339</v>
       </c>
       <c r="W68">
-        <v>0.2389276063386155</v>
+        <v>0.2388809256469944</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6884,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.05305523899262954</v>
+        <v>-0.05226336975393364</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6892,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2584128409987367</v>
+        <v>0.2603128409987367</v>
       </c>
       <c r="C69">
-        <v>-3.665408031257487</v>
+        <v>-3.823118796817476</v>
       </c>
       <c r="D69">
-        <v>4.268891968742514</v>
+        <v>4.231081203182524</v>
       </c>
       <c r="E69">
-        <v>1.403300000000001</v>
+        <v>1.5232</v>
       </c>
       <c r="F69">
-        <v>8.033300000000001</v>
+        <v>8.1532</v>
       </c>
       <c r="G69">
         <v>0.099</v>
@@ -6928,37 +6939,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M69">
-        <v>1.89425214</v>
+        <v>1.92252456</v>
       </c>
       <c r="N69">
-        <v>-1.99325214</v>
+        <v>-2.02152456</v>
       </c>
       <c r="O69">
-        <v>-0.4983130350000001</v>
+        <v>-0.50538114</v>
       </c>
       <c r="P69">
-        <v>-1.494939105</v>
+        <v>-1.51614342</v>
       </c>
       <c r="Q69">
-        <v>-0.9299391050000003</v>
+        <v>-0.9511434200000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2980685479250014</v>
+        <v>0.3059519400476577</v>
       </c>
       <c r="T69">
-        <v>3.90251420538746</v>
+        <v>4.024467774305818</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.01306584243848339</v>
+        <v>-0.01287369769674099</v>
       </c>
       <c r="W69">
-        <v>0.2388809256469944</v>
+        <v>0.2388356179168915</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6966,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.05226336975393364</v>
+        <v>-0.05149479078696406</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6974,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2603128409987367</v>
+        <v>0.2622128409987367</v>
       </c>
       <c r="C70">
-        <v>-3.823118796817476</v>
+        <v>-3.98016564193511</v>
       </c>
       <c r="D70">
-        <v>4.231081203182524</v>
+        <v>4.193934358064891</v>
       </c>
       <c r="E70">
-        <v>1.5232</v>
+        <v>1.643100000000001</v>
       </c>
       <c r="F70">
-        <v>8.1532</v>
+        <v>8.273100000000001</v>
       </c>
       <c r="G70">
         <v>0.099</v>
@@ -7010,37 +7021,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M70">
-        <v>1.92252456</v>
+        <v>1.95079698</v>
       </c>
       <c r="N70">
-        <v>-2.02152456</v>
+        <v>-2.04979698</v>
       </c>
       <c r="O70">
-        <v>-0.50538114</v>
+        <v>-0.5124492450000001</v>
       </c>
       <c r="P70">
-        <v>-1.51614342</v>
+        <v>-1.537347735</v>
       </c>
       <c r="Q70">
-        <v>-0.9511434200000002</v>
+        <v>-0.9723477350000005</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3059519400476577</v>
+        <v>0.3143439381137113</v>
       </c>
       <c r="T70">
-        <v>4.024467774305818</v>
+        <v>4.154289315412458</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.01287369769674099</v>
+        <v>-0.01268712236780271</v>
       </c>
       <c r="W70">
-        <v>0.2388356179168915</v>
+        <v>0.2387916234543279</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7048,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.05149479078696406</v>
+        <v>-0.05074848947121091</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7056,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2622128409987367</v>
+        <v>0.2641128409987367</v>
       </c>
       <c r="C71">
-        <v>-3.98016564193511</v>
+        <v>-4.136565901122196</v>
       </c>
       <c r="D71">
-        <v>4.193934358064891</v>
+        <v>4.157434098877805</v>
       </c>
       <c r="E71">
-        <v>1.643100000000001</v>
+        <v>1.763000000000001</v>
       </c>
       <c r="F71">
-        <v>8.273100000000001</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="G71">
         <v>0.099</v>
@@ -7092,37 +7103,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M71">
-        <v>1.95079698</v>
+        <v>1.9790694</v>
       </c>
       <c r="N71">
-        <v>-2.04979698</v>
+        <v>-2.0780694</v>
       </c>
       <c r="O71">
-        <v>-0.5124492450000001</v>
+        <v>-0.51951735</v>
       </c>
       <c r="P71">
-        <v>-1.537347735</v>
+        <v>-1.55855205</v>
       </c>
       <c r="Q71">
-        <v>-0.9723477350000005</v>
+        <v>-0.9935520499999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3143439381137113</v>
+        <v>0.3232954027175016</v>
       </c>
       <c r="T71">
-        <v>4.154289315412458</v>
+        <v>4.292765625926206</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.01268712236780271</v>
+        <v>-0.01250587776254839</v>
       </c>
       <c r="W71">
-        <v>0.2387916234543279</v>
+        <v>0.2387488859764089</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7130,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.05074848947121091</v>
+        <v>-0.05002351105019343</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7138,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2641128409987367</v>
+        <v>0.2660128409987367</v>
       </c>
       <c r="C72">
-        <v>-4.136565901122196</v>
+        <v>-4.292336310640746</v>
       </c>
       <c r="D72">
-        <v>4.157434098877805</v>
+        <v>4.121563689359256</v>
       </c>
       <c r="E72">
-        <v>1.763000000000001</v>
+        <v>1.882900000000002</v>
       </c>
       <c r="F72">
-        <v>8.393000000000001</v>
+        <v>8.512900000000002</v>
       </c>
       <c r="G72">
         <v>0.099</v>
@@ -7174,37 +7185,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M72">
-        <v>1.9790694</v>
+        <v>2.007341820000001</v>
       </c>
       <c r="N72">
-        <v>-2.0780694</v>
+        <v>-2.10634182</v>
       </c>
       <c r="O72">
-        <v>-0.51951735</v>
+        <v>-0.5265854550000001</v>
       </c>
       <c r="P72">
-        <v>-1.55855205</v>
+        <v>-1.579756365</v>
       </c>
       <c r="Q72">
-        <v>-0.9935520499999999</v>
+        <v>-1.014756365</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3232954027175016</v>
+        <v>0.3328642097077603</v>
       </c>
       <c r="T72">
-        <v>4.292765625926206</v>
+        <v>4.440792026820214</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.01250587776254839</v>
+        <v>-0.01232973863913221</v>
       </c>
       <c r="W72">
-        <v>0.2387488859764089</v>
+        <v>0.2387073523711074</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7212,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.05002351105019343</v>
+        <v>-0.04931895455652868</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7220,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2660128409987367</v>
+        <v>0.2679128409987367</v>
       </c>
       <c r="C73">
-        <v>-4.292336310640744</v>
+        <v>-4.447493034090727</v>
       </c>
       <c r="D73">
-        <v>4.121563689359256</v>
+        <v>4.086306965909272</v>
       </c>
       <c r="E73">
-        <v>1.8829</v>
+        <v>2.0028</v>
       </c>
       <c r="F73">
-        <v>8.5129</v>
+        <v>8.6328</v>
       </c>
       <c r="G73">
         <v>0.099</v>
@@ -7256,37 +7267,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M73">
-        <v>2.00734182</v>
+        <v>2.03561424</v>
       </c>
       <c r="N73">
-        <v>-2.10634182</v>
+        <v>-2.13461424</v>
       </c>
       <c r="O73">
-        <v>-0.526585455</v>
+        <v>-0.53365356</v>
       </c>
       <c r="P73">
-        <v>-1.579756365</v>
+        <v>-1.60096068</v>
       </c>
       <c r="Q73">
-        <v>-1.014756365</v>
+        <v>-1.03596068</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3328642097077602</v>
+        <v>0.3431165029116088</v>
       </c>
       <c r="T73">
-        <v>4.440792026820212</v>
+        <v>4.599391742063792</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.01232973863913221</v>
+        <v>-0.01215849226914427</v>
       </c>
       <c r="W73">
-        <v>0.2387073523711074</v>
+        <v>0.2386669724770642</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7294,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.04931895455652868</v>
+        <v>-0.04863396907657691</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7302,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2679128409987367</v>
+        <v>0.2698128409987367</v>
       </c>
       <c r="C74">
-        <v>-4.447493034090727</v>
+        <v>-4.602051686695699</v>
       </c>
       <c r="D74">
-        <v>4.086306965909272</v>
+        <v>4.051648313304302</v>
       </c>
       <c r="E74">
-        <v>2.0028</v>
+        <v>2.122700000000001</v>
       </c>
       <c r="F74">
-        <v>8.6328</v>
+        <v>8.752700000000001</v>
       </c>
       <c r="G74">
         <v>0.099</v>
@@ -7338,37 +7349,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M74">
-        <v>2.03561424</v>
+        <v>2.06388666</v>
       </c>
       <c r="N74">
-        <v>-2.13461424</v>
+        <v>-2.16288666</v>
       </c>
       <c r="O74">
-        <v>-0.53365356</v>
+        <v>-0.540721665</v>
       </c>
       <c r="P74">
-        <v>-1.60096068</v>
+        <v>-1.622164995</v>
       </c>
       <c r="Q74">
-        <v>-1.03596068</v>
+        <v>-1.057164995</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3431165029116088</v>
+        <v>0.3541282252416684</v>
       </c>
       <c r="T74">
-        <v>4.599391742063792</v>
+        <v>4.76973958436245</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.01215849226914427</v>
+        <v>-0.01199193758052585</v>
       </c>
       <c r="W74">
-        <v>0.2386669724770642</v>
+        <v>0.238627698881488</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7376,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.04863396907657691</v>
+        <v>-0.04796775032210343</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7384,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2698128409987367</v>
+        <v>0.2717128409987367</v>
       </c>
       <c r="C75">
-        <v>-4.602051686695699</v>
+        <v>-4.756027358362902</v>
       </c>
       <c r="D75">
-        <v>4.051648313304302</v>
+        <v>4.017572641637098</v>
       </c>
       <c r="E75">
-        <v>2.122700000000001</v>
+        <v>2.2426</v>
       </c>
       <c r="F75">
-        <v>8.752700000000001</v>
+        <v>8.8726</v>
       </c>
       <c r="G75">
         <v>0.099</v>
@@ -7420,37 +7431,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M75">
-        <v>2.06388666</v>
+        <v>2.09215908</v>
       </c>
       <c r="N75">
-        <v>-2.16288666</v>
+        <v>-2.19115908</v>
       </c>
       <c r="O75">
-        <v>-0.540721665</v>
+        <v>-0.54778977</v>
       </c>
       <c r="P75">
-        <v>-1.622164995</v>
+        <v>-1.64336931</v>
       </c>
       <c r="Q75">
-        <v>-1.057164995</v>
+        <v>-1.07836931</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3541282252416684</v>
+        <v>0.3659870031355787</v>
       </c>
       <c r="T75">
-        <v>4.76973958436245</v>
+        <v>4.953191106837929</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.01199193758052585</v>
+        <v>-0.0118298843699782</v>
       </c>
       <c r="W75">
-        <v>0.238627698881488</v>
+        <v>0.2385894867344409</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7458,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.04796775032210343</v>
+        <v>-0.04731953747991269</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7466,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2717128409987367</v>
+        <v>0.2736128409987367</v>
       </c>
       <c r="C76">
-        <v>-4.756027358362902</v>
+        <v>-4.909434635589442</v>
       </c>
       <c r="D76">
-        <v>4.017572641637098</v>
+        <v>3.984065364410557</v>
       </c>
       <c r="E76">
-        <v>2.2426</v>
+        <v>2.3625</v>
       </c>
       <c r="F76">
-        <v>8.8726</v>
+        <v>8.9925</v>
       </c>
       <c r="G76">
         <v>0.099</v>
@@ -7502,37 +7513,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M76">
-        <v>2.09215908</v>
+        <v>2.1204315</v>
       </c>
       <c r="N76">
-        <v>-2.19115908</v>
+        <v>-2.2194315</v>
       </c>
       <c r="O76">
-        <v>-0.54778977</v>
+        <v>-0.5548578749999999</v>
       </c>
       <c r="P76">
-        <v>-1.64336931</v>
+        <v>-1.664573625</v>
       </c>
       <c r="Q76">
-        <v>-1.07836931</v>
+        <v>-1.099573625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3659870031355787</v>
+        <v>0.3787944832610019</v>
       </c>
       <c r="T76">
-        <v>4.953191106837929</v>
+        <v>5.151318751111448</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.0118298843699782</v>
+        <v>-0.0116721525783785</v>
       </c>
       <c r="W76">
-        <v>0.2385894867344409</v>
+        <v>0.2385522935779817</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7540,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.04731953747991269</v>
+        <v>-0.04668861031351401</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7548,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2736128409987367</v>
+        <v>0.2755128409987367</v>
       </c>
       <c r="C77">
-        <v>-4.909434635589442</v>
+        <v>-5.062287622281302</v>
       </c>
       <c r="D77">
-        <v>3.984065364410557</v>
+        <v>3.9511123777187</v>
       </c>
       <c r="E77">
-        <v>2.3625</v>
+        <v>2.482400000000001</v>
       </c>
       <c r="F77">
-        <v>8.9925</v>
+        <v>9.112400000000001</v>
       </c>
       <c r="G77">
         <v>0.099</v>
@@ -7584,37 +7595,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M77">
-        <v>2.1204315</v>
+        <v>2.14870392</v>
       </c>
       <c r="N77">
-        <v>-2.2194315</v>
+        <v>-2.24770392</v>
       </c>
       <c r="O77">
-        <v>-0.5548578749999999</v>
+        <v>-0.56192598</v>
       </c>
       <c r="P77">
-        <v>-1.664573625</v>
+        <v>-1.68577794</v>
       </c>
       <c r="Q77">
-        <v>-1.099573625</v>
+        <v>-1.12077794</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3787944832610019</v>
+        <v>0.392669253396877</v>
       </c>
       <c r="T77">
-        <v>5.151318751111448</v>
+        <v>5.365957032407758</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.0116721525783785</v>
+        <v>-0.01151857162339983</v>
       </c>
       <c r="W77">
-        <v>0.2385522935779817</v>
+        <v>0.2385160791887977</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7622,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.04668861031351401</v>
+        <v>-0.04607428649359924</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7630,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2755128409987367</v>
+        <v>0.2774128409987368</v>
       </c>
       <c r="C78">
-        <v>-5.062287622281302</v>
+        <v>-5.214599959547638</v>
       </c>
       <c r="D78">
-        <v>3.9511123777187</v>
+        <v>3.918700040452363</v>
       </c>
       <c r="E78">
-        <v>2.482400000000001</v>
+        <v>2.602300000000001</v>
       </c>
       <c r="F78">
-        <v>9.112400000000001</v>
+        <v>9.2323</v>
       </c>
       <c r="G78">
         <v>0.099</v>
@@ -7666,37 +7677,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M78">
-        <v>2.14870392</v>
+        <v>2.17697634</v>
       </c>
       <c r="N78">
-        <v>-2.24770392</v>
+        <v>-2.27597634</v>
       </c>
       <c r="O78">
-        <v>-0.56192598</v>
+        <v>-0.568994085</v>
       </c>
       <c r="P78">
-        <v>-1.68577794</v>
+        <v>-1.706982255</v>
       </c>
       <c r="Q78">
-        <v>-1.12077794</v>
+        <v>-1.141982255</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.392669253396877</v>
+        <v>0.4077505252836977</v>
       </c>
       <c r="T78">
-        <v>5.365957032407758</v>
+        <v>5.59925951207766</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.01151857162339983</v>
+        <v>-0.0113689797841349</v>
       </c>
       <c r="W78">
-        <v>0.2385160791887977</v>
+        <v>0.238480805433099</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7704,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.04607428649359924</v>
+        <v>-0.04547591913653948</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7712,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2774128409987368</v>
+        <v>0.2793128409987367</v>
       </c>
       <c r="C79">
-        <v>-5.214599959547638</v>
+        <v>-5.366384844528757</v>
       </c>
       <c r="D79">
-        <v>3.918700040452363</v>
+        <v>3.886815155471242</v>
       </c>
       <c r="E79">
-        <v>2.602300000000001</v>
+        <v>2.7222</v>
       </c>
       <c r="F79">
-        <v>9.2323</v>
+        <v>9.3522</v>
       </c>
       <c r="G79">
         <v>0.099</v>
@@ -7748,37 +7759,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M79">
-        <v>2.17697634</v>
+        <v>2.20524876</v>
       </c>
       <c r="N79">
-        <v>-2.27597634</v>
+        <v>-2.30424876</v>
       </c>
       <c r="O79">
-        <v>-0.568994085</v>
+        <v>-0.5760621899999999</v>
       </c>
       <c r="P79">
-        <v>-1.706982255</v>
+        <v>-1.72818657</v>
       </c>
       <c r="Q79">
-        <v>-1.141982255</v>
+        <v>-1.16318657</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4077505252836977</v>
+        <v>0.4242028218875021</v>
       </c>
       <c r="T79">
-        <v>5.59925951207766</v>
+        <v>5.85377130808119</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.0113689797841349</v>
+        <v>-0.01122322363305625</v>
       </c>
       <c r="W79">
-        <v>0.238480805433099</v>
+        <v>0.2384464361326747</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7786,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.04547591913653948</v>
+        <v>-0.04489289453222489</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7794,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2793128409987367</v>
+        <v>0.2812128409987368</v>
       </c>
       <c r="C80">
-        <v>-5.366384844528757</v>
+        <v>-5.517655048312312</v>
       </c>
       <c r="D80">
-        <v>3.886815155471242</v>
+        <v>3.855444951687689</v>
       </c>
       <c r="E80">
-        <v>2.7222</v>
+        <v>2.842100000000001</v>
       </c>
       <c r="F80">
-        <v>9.3522</v>
+        <v>9.472100000000001</v>
       </c>
       <c r="G80">
         <v>0.099</v>
@@ -7830,37 +7841,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M80">
-        <v>2.20524876</v>
+        <v>2.23352118</v>
       </c>
       <c r="N80">
-        <v>-2.30424876</v>
+        <v>-2.33252118</v>
       </c>
       <c r="O80">
-        <v>-0.5760621899999999</v>
+        <v>-0.583130295</v>
       </c>
       <c r="P80">
-        <v>-1.72818657</v>
+        <v>-1.749390885</v>
       </c>
       <c r="Q80">
-        <v>-1.16318657</v>
+        <v>-1.184390885</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4242028218875021</v>
+        <v>0.4422220038821452</v>
       </c>
       <c r="T80">
-        <v>5.85377130808119</v>
+        <v>6.132522322751724</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.01122322363305625</v>
+        <v>-0.01108115751111882</v>
       </c>
       <c r="W80">
-        <v>0.2384464361326747</v>
+        <v>0.2384129369411219</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7868,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.04489289453222489</v>
+        <v>-0.04432463004447529</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7876,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2812128409987368</v>
+        <v>0.2831128409987367</v>
       </c>
       <c r="C81">
-        <v>-5.517655048312312</v>
+        <v>-5.668422932988832</v>
       </c>
       <c r="D81">
-        <v>3.855444951687689</v>
+        <v>3.824577067011168</v>
       </c>
       <c r="E81">
-        <v>2.842100000000001</v>
+        <v>2.962000000000001</v>
       </c>
       <c r="F81">
-        <v>9.472100000000001</v>
+        <v>9.592000000000001</v>
       </c>
       <c r="G81">
         <v>0.099</v>
@@ -7912,37 +7923,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M81">
-        <v>2.23352118</v>
+        <v>2.2617936</v>
       </c>
       <c r="N81">
-        <v>-2.33252118</v>
+        <v>-2.3607936</v>
       </c>
       <c r="O81">
-        <v>-0.583130295</v>
+        <v>-0.5901984</v>
       </c>
       <c r="P81">
-        <v>-1.749390885</v>
+        <v>-1.7705952</v>
       </c>
       <c r="Q81">
-        <v>-1.184390885</v>
+        <v>-1.2055952</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4422220038821452</v>
+        <v>0.4620431040762524</v>
       </c>
       <c r="T81">
-        <v>6.132522322751724</v>
+        <v>6.43914843888931</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.01108115751111882</v>
+        <v>-0.01094264304222984</v>
       </c>
       <c r="W81">
-        <v>0.2384129369411219</v>
+        <v>0.2383802752293578</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7950,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.04432463004447529</v>
+        <v>-0.04377057216891922</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7958,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2831128409987367</v>
+        <v>0.2850128409987367</v>
       </c>
       <c r="C82">
-        <v>-5.668422932988832</v>
+        <v>-5.818700467894491</v>
       </c>
       <c r="D82">
-        <v>3.824577067011168</v>
+        <v>3.794199532105508</v>
       </c>
       <c r="E82">
-        <v>2.962000000000001</v>
+        <v>3.0819</v>
       </c>
       <c r="F82">
-        <v>9.592000000000001</v>
+        <v>9.7119</v>
       </c>
       <c r="G82">
         <v>0.099</v>
@@ -7994,37 +8005,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M82">
-        <v>2.2617936</v>
+        <v>2.29006602</v>
       </c>
       <c r="N82">
-        <v>-2.3607936</v>
+        <v>-2.38906602</v>
       </c>
       <c r="O82">
-        <v>-0.5901984</v>
+        <v>-0.597266505</v>
       </c>
       <c r="P82">
-        <v>-1.7705952</v>
+        <v>-1.791799515</v>
       </c>
       <c r="Q82">
-        <v>-1.2055952</v>
+        <v>-1.226799515</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4620431040762524</v>
+        <v>0.4839506358697394</v>
       </c>
       <c r="T82">
-        <v>6.43914843888931</v>
+        <v>6.778050988304537</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.01094264304222984</v>
+        <v>-0.01080754868368379</v>
       </c>
       <c r="W82">
-        <v>0.2383802752293578</v>
+        <v>0.2383484199796126</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8032,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.04377057216891922</v>
+        <v>-0.04323019473473511</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8040,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2850128409987367</v>
+        <v>0.2869128409987367</v>
       </c>
       <c r="C83">
-        <v>-5.818700467894491</v>
+        <v>-5.968499245085867</v>
       </c>
       <c r="D83">
-        <v>3.794199532105508</v>
+        <v>3.764300754914134</v>
       </c>
       <c r="E83">
-        <v>3.0819</v>
+        <v>3.201800000000001</v>
       </c>
       <c r="F83">
-        <v>9.7119</v>
+        <v>9.831800000000001</v>
       </c>
       <c r="G83">
         <v>0.099</v>
@@ -8076,37 +8087,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M83">
-        <v>2.29006602</v>
+        <v>2.31833844</v>
       </c>
       <c r="N83">
-        <v>-2.38906602</v>
+        <v>-2.41733844</v>
       </c>
       <c r="O83">
-        <v>-0.597266505</v>
+        <v>-0.60433461</v>
       </c>
       <c r="P83">
-        <v>-1.791799515</v>
+        <v>-1.81300383</v>
       </c>
       <c r="Q83">
-        <v>-1.226799515</v>
+        <v>-1.24800383</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4839506358697394</v>
+        <v>0.5082923378625027</v>
       </c>
       <c r="T83">
-        <v>6.778050988304537</v>
+        <v>7.154609376543678</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.01080754868368379</v>
+        <v>-0.01067574930949253</v>
       </c>
       <c r="W83">
-        <v>0.2383484199796126</v>
+        <v>0.2383173416871783</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8114,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.04323019473473511</v>
+        <v>-0.04270299723797</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8122,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2869128409987367</v>
+        <v>0.2888128409987367</v>
       </c>
       <c r="C84">
-        <v>-5.968499245085867</v>
+        <v>-6.11783049408877</v>
       </c>
       <c r="D84">
-        <v>3.764300754914134</v>
+        <v>3.734869505911231</v>
       </c>
       <c r="E84">
-        <v>3.201800000000001</v>
+        <v>3.321700000000001</v>
       </c>
       <c r="F84">
-        <v>9.831800000000001</v>
+        <v>9.951700000000001</v>
       </c>
       <c r="G84">
         <v>0.099</v>
@@ -8158,37 +8169,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M84">
-        <v>2.31833844</v>
+        <v>2.34661086</v>
       </c>
       <c r="N84">
-        <v>-2.41733844</v>
+        <v>-2.44561086</v>
       </c>
       <c r="O84">
-        <v>-0.60433461</v>
+        <v>-0.611402715</v>
       </c>
       <c r="P84">
-        <v>-1.81300383</v>
+        <v>-1.834208145</v>
       </c>
       <c r="Q84">
-        <v>-1.24800383</v>
+        <v>-1.269208145</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5082923378625027</v>
+        <v>0.5354977695014735</v>
       </c>
       <c r="T84">
-        <v>7.154609376543678</v>
+        <v>7.575468751634483</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.01067574930949253</v>
+        <v>-0.01054712582383599</v>
       </c>
       <c r="W84">
-        <v>0.2383173416871783</v>
+        <v>0.2382870122692605</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8196,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.04270299723797</v>
+        <v>-0.04218850329534396</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8204,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2888128409987367</v>
+        <v>0.2907128409987367</v>
       </c>
       <c r="C85">
-        <v>-6.11783049408877</v>
+        <v>-6.266705095960576</v>
       </c>
       <c r="D85">
-        <v>3.734869505911231</v>
+        <v>3.705894904039425</v>
       </c>
       <c r="E85">
-        <v>3.321700000000001</v>
+        <v>3.441600000000002</v>
       </c>
       <c r="F85">
-        <v>9.951700000000001</v>
+        <v>10.0716</v>
       </c>
       <c r="G85">
         <v>0.099</v>
@@ -8240,37 +8251,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M85">
-        <v>2.34661086</v>
+        <v>2.374883280000001</v>
       </c>
       <c r="N85">
-        <v>-2.44561086</v>
+        <v>-2.47388328</v>
       </c>
       <c r="O85">
-        <v>-0.611402715</v>
+        <v>-0.6184708200000001</v>
       </c>
       <c r="P85">
-        <v>-1.834208145</v>
+        <v>-1.85541246</v>
       </c>
       <c r="Q85">
-        <v>-1.269208145</v>
+        <v>-1.29041246</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5354977695014735</v>
+        <v>0.5661038800953158</v>
       </c>
       <c r="T85">
-        <v>7.575468751634483</v>
+        <v>8.048935548611642</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.01054712582383599</v>
+        <v>-0.01042156480212365</v>
       </c>
       <c r="W85">
-        <v>0.2382870122692605</v>
+        <v>0.2382574049803408</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8278,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.04218850329534396</v>
+        <v>-0.04168625920849456</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8286,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2907128409987367</v>
+        <v>0.2926128409987367</v>
       </c>
       <c r="C86">
-        <v>-6.266705095960575</v>
+        <v>-6.415133596703009</v>
       </c>
       <c r="D86">
-        <v>3.705894904039425</v>
+        <v>3.677366403296991</v>
       </c>
       <c r="E86">
-        <v>3.4416</v>
+        <v>3.5615</v>
       </c>
       <c r="F86">
-        <v>10.0716</v>
+        <v>10.1915</v>
       </c>
       <c r="G86">
         <v>0.099</v>
@@ -8322,37 +8333,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M86">
-        <v>2.37488328</v>
+        <v>2.4031557</v>
       </c>
       <c r="N86">
-        <v>-2.47388328</v>
+        <v>-2.5021557</v>
       </c>
       <c r="O86">
-        <v>-0.61847082</v>
+        <v>-0.625538925</v>
       </c>
       <c r="P86">
-        <v>-1.85541246</v>
+        <v>-1.876616775</v>
       </c>
       <c r="Q86">
-        <v>-1.29041246</v>
+        <v>-1.311616775</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5661038800953154</v>
+        <v>0.6007908054350029</v>
       </c>
       <c r="T86">
-        <v>8.048935548611636</v>
+        <v>8.585531251852409</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.01042156480212366</v>
+        <v>-0.01029895815739279</v>
       </c>
       <c r="W86">
-        <v>0.2382574049803408</v>
+        <v>0.2382284943335132</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8360,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.04168625920849456</v>
+        <v>-0.04119583262957116</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8368,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2926128409987367</v>
+        <v>0.2945128409987367</v>
       </c>
       <c r="C87">
-        <v>-6.415133596703009</v>
+        <v>-6.563126220060161</v>
       </c>
       <c r="D87">
-        <v>3.677366403296991</v>
+        <v>3.64927377993984</v>
       </c>
       <c r="E87">
-        <v>3.5615</v>
+        <v>3.681400000000001</v>
       </c>
       <c r="F87">
-        <v>10.1915</v>
+        <v>10.3114</v>
       </c>
       <c r="G87">
         <v>0.099</v>
@@ -8404,37 +8415,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M87">
-        <v>2.4031557</v>
+        <v>2.43142812</v>
       </c>
       <c r="N87">
-        <v>-2.5021557</v>
+        <v>-2.53042812</v>
       </c>
       <c r="O87">
-        <v>-0.625538925</v>
+        <v>-0.63260703</v>
       </c>
       <c r="P87">
-        <v>-1.876616775</v>
+        <v>-1.89782109</v>
       </c>
       <c r="Q87">
-        <v>-1.311616775</v>
+        <v>-1.33282109</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6007908054350029</v>
+        <v>0.6404330058232175</v>
       </c>
       <c r="T87">
-        <v>8.585531251852409</v>
+        <v>9.198783484127583</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.01029895815739279</v>
+        <v>-0.01017920282998125</v>
       </c>
       <c r="W87">
-        <v>0.2382284943335132</v>
+        <v>0.2382002560273096</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8442,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.04119583262957116</v>
+        <v>-0.04071681131992499</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8450,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2945128409987367</v>
+        <v>0.2964128409987367</v>
       </c>
       <c r="C88">
-        <v>-6.563126220060161</v>
+        <v>-6.710692879734317</v>
       </c>
       <c r="D88">
-        <v>3.64927377993984</v>
+        <v>3.621607120265682</v>
       </c>
       <c r="E88">
-        <v>3.681400000000001</v>
+        <v>3.8013</v>
       </c>
       <c r="F88">
-        <v>10.3114</v>
+        <v>10.4313</v>
       </c>
       <c r="G88">
         <v>0.099</v>
@@ -8486,37 +8497,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M88">
-        <v>2.43142812</v>
+        <v>2.45970054</v>
       </c>
       <c r="N88">
-        <v>-2.53042812</v>
+        <v>-2.55870054</v>
       </c>
       <c r="O88">
-        <v>-0.63260703</v>
+        <v>-0.639675135</v>
       </c>
       <c r="P88">
-        <v>-1.89782109</v>
+        <v>-1.919025405</v>
       </c>
       <c r="Q88">
-        <v>-1.33282109</v>
+        <v>-1.354025405</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6404330058232175</v>
+        <v>0.6861740062711573</v>
       </c>
       <c r="T88">
-        <v>9.198783484127583</v>
+        <v>9.906382213675858</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.01017920282998125</v>
+        <v>-0.01006220049860215</v>
       </c>
       <c r="W88">
-        <v>0.2382002560273096</v>
+        <v>0.2381726668775704</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8524,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.04071681131992499</v>
+        <v>-0.0402488019944085</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8532,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2964128409987367</v>
+        <v>0.2983128409987367</v>
       </c>
       <c r="C89">
-        <v>-6.710692879734317</v>
+        <v>-6.857843191050323</v>
       </c>
       <c r="D89">
-        <v>3.621607120265682</v>
+        <v>3.594356808949677</v>
       </c>
       <c r="E89">
-        <v>3.8013</v>
+        <v>3.9212</v>
       </c>
       <c r="F89">
-        <v>10.4313</v>
+        <v>10.5512</v>
       </c>
       <c r="G89">
         <v>0.099</v>
@@ -8568,37 +8579,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M89">
-        <v>2.45970054</v>
+        <v>2.48797296</v>
       </c>
       <c r="N89">
-        <v>-2.55870054</v>
+        <v>-2.58697296</v>
       </c>
       <c r="O89">
-        <v>-0.639675135</v>
+        <v>-0.6467432399999999</v>
       </c>
       <c r="P89">
-        <v>-1.919025405</v>
+        <v>-1.94022972</v>
       </c>
       <c r="Q89">
-        <v>-1.354025405</v>
+        <v>-1.37522972</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6861740062711573</v>
+        <v>0.739538506793754</v>
       </c>
       <c r="T89">
-        <v>9.906382213675858</v>
+        <v>10.73191406481552</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.01006220049860215</v>
+        <v>-0.009947857311118035</v>
       </c>
       <c r="W89">
-        <v>0.2381726668775704</v>
+        <v>0.2381457047539616</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8606,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.0402488019944085</v>
+        <v>-0.0397914292444721</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8614,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2983128409987367</v>
+        <v>0.3002128409987367</v>
       </c>
       <c r="C90">
-        <v>-6.857843191050323</v>
+        <v>-7.004586482097249</v>
       </c>
       <c r="D90">
-        <v>3.594356808949677</v>
+        <v>3.567513517902751</v>
       </c>
       <c r="E90">
-        <v>3.9212</v>
+        <v>4.041100000000001</v>
       </c>
       <c r="F90">
-        <v>10.5512</v>
+        <v>10.6711</v>
       </c>
       <c r="G90">
         <v>0.099</v>
@@ -8650,37 +8661,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M90">
-        <v>2.48797296</v>
+        <v>2.51624538</v>
       </c>
       <c r="N90">
-        <v>-2.58697296</v>
+        <v>-2.61524538</v>
       </c>
       <c r="O90">
-        <v>-0.6467432399999999</v>
+        <v>-0.653811345</v>
       </c>
       <c r="P90">
-        <v>-1.94022972</v>
+        <v>-1.961434035</v>
       </c>
       <c r="Q90">
-        <v>-1.37522972</v>
+        <v>-1.396434035</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.739538506793754</v>
+        <v>0.8026056437750042</v>
       </c>
       <c r="T90">
-        <v>10.73191406481552</v>
+        <v>11.70754261616238</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.009947857311118035</v>
+        <v>-0.009836083633465022</v>
       </c>
       <c r="W90">
-        <v>0.2381457047539616</v>
+        <v>0.238119348520771</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8688,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.0397914292444721</v>
+        <v>-0.03934433453385999</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8696,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3002128409987367</v>
+        <v>0.3021128409987367</v>
       </c>
       <c r="C91">
-        <v>-7.004586482097249</v>
+        <v>-7.150931804374522</v>
       </c>
       <c r="D91">
-        <v>3.567513517902751</v>
+        <v>3.541068195625477</v>
       </c>
       <c r="E91">
-        <v>4.041100000000001</v>
+        <v>4.161</v>
       </c>
       <c r="F91">
-        <v>10.6711</v>
+        <v>10.791</v>
       </c>
       <c r="G91">
         <v>0.099</v>
@@ -8732,37 +8743,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M91">
-        <v>2.51624538</v>
+        <v>2.5445178</v>
       </c>
       <c r="N91">
-        <v>-2.61524538</v>
+        <v>-2.6435178</v>
       </c>
       <c r="O91">
-        <v>-0.653811345</v>
+        <v>-0.66087945</v>
       </c>
       <c r="P91">
-        <v>-1.961434035</v>
+        <v>-1.98263835</v>
       </c>
       <c r="Q91">
-        <v>-1.396434035</v>
+        <v>-1.41763835</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8026056437750042</v>
+        <v>0.8782862081525048</v>
       </c>
       <c r="T91">
-        <v>11.70754261616238</v>
+        <v>12.87829687777862</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.009836083633465022</v>
+        <v>-0.009726793815315412</v>
       </c>
       <c r="W91">
-        <v>0.238119348520771</v>
+        <v>0.2380935779816514</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8770,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.03934433453385999</v>
+        <v>-0.03890717526126153</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8778,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3021128409987367</v>
+        <v>0.3040128409987367</v>
       </c>
       <c r="C92">
-        <v>-7.150931804374522</v>
+        <v>-7.296887942968039</v>
       </c>
       <c r="D92">
-        <v>3.541068195625477</v>
+        <v>3.515012057031961</v>
       </c>
       <c r="E92">
-        <v>4.161</v>
+        <v>4.2809</v>
       </c>
       <c r="F92">
-        <v>10.791</v>
+        <v>10.9109</v>
       </c>
       <c r="G92">
         <v>0.099</v>
@@ -8814,37 +8825,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M92">
-        <v>2.5445178</v>
+        <v>2.57279022</v>
       </c>
       <c r="N92">
-        <v>-2.6435178</v>
+        <v>-2.67179022</v>
       </c>
       <c r="O92">
-        <v>-0.66087945</v>
+        <v>-0.6679475549999999</v>
       </c>
       <c r="P92">
-        <v>-1.98263835</v>
+        <v>-2.003842665</v>
       </c>
       <c r="Q92">
-        <v>-1.41763835</v>
+        <v>-1.438842665</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8782862081525048</v>
+        <v>0.9707846757250054</v>
       </c>
       <c r="T92">
-        <v>12.87829687777862</v>
+        <v>14.30921875308736</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.009726793815315412</v>
+        <v>-0.009619905971191068</v>
       </c>
       <c r="W92">
-        <v>0.2380935779816514</v>
+        <v>0.2380683738280069</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8852,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.03890717526126153</v>
+        <v>-0.03847962388476422</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8860,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3040128409987367</v>
+        <v>0.3059128409987367</v>
       </c>
       <c r="C93">
-        <v>-7.296887942968039</v>
+        <v>-7.442463426280273</v>
       </c>
       <c r="D93">
-        <v>3.515012057031961</v>
+        <v>3.489336573719727</v>
       </c>
       <c r="E93">
-        <v>4.2809</v>
+        <v>4.400800000000001</v>
       </c>
       <c r="F93">
-        <v>10.9109</v>
+        <v>11.0308</v>
       </c>
       <c r="G93">
         <v>0.099</v>
@@ -8896,37 +8907,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M93">
-        <v>2.57279022</v>
+        <v>2.60106264</v>
       </c>
       <c r="N93">
-        <v>-2.67179022</v>
+        <v>-2.70006264</v>
       </c>
       <c r="O93">
-        <v>-0.6679475549999999</v>
+        <v>-0.67501566</v>
       </c>
       <c r="P93">
-        <v>-2.003842665</v>
+        <v>-2.02504698</v>
       </c>
       <c r="Q93">
-        <v>-1.438842665</v>
+        <v>-1.46004698</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9707846757250054</v>
+        <v>1.086407760190631</v>
       </c>
       <c r="T93">
-        <v>14.30921875308736</v>
+        <v>16.09787109722328</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.009619905971191068</v>
+        <v>-0.009515341775852034</v>
       </c>
       <c r="W93">
-        <v>0.2380683738280069</v>
+        <v>0.2380437175907459</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8934,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.03847962388476422</v>
+        <v>-0.03806136710340802</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8942,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3059128409987367</v>
+        <v>0.3078128409987367</v>
       </c>
       <c r="C94">
-        <v>-7.442463426280273</v>
+        <v>-7.587666535337052</v>
       </c>
       <c r="D94">
-        <v>3.489336573719727</v>
+        <v>3.464033464662948</v>
       </c>
       <c r="E94">
-        <v>4.400800000000001</v>
+        <v>4.520700000000001</v>
       </c>
       <c r="F94">
-        <v>11.0308</v>
+        <v>11.1507</v>
       </c>
       <c r="G94">
         <v>0.099</v>
@@ -8978,37 +8989,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M94">
-        <v>2.60106264</v>
+        <v>2.62933506</v>
       </c>
       <c r="N94">
-        <v>-2.70006264</v>
+        <v>-2.72833506</v>
       </c>
       <c r="O94">
-        <v>-0.67501566</v>
+        <v>-0.682083765</v>
       </c>
       <c r="P94">
-        <v>-2.02504698</v>
+        <v>-2.046251295</v>
       </c>
       <c r="Q94">
-        <v>-1.46004698</v>
+        <v>-1.481251295</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.086407760190631</v>
+        <v>1.235066011646436</v>
       </c>
       <c r="T94">
-        <v>16.09787109722328</v>
+        <v>18.39756696825518</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.009515341775852034</v>
+        <v>-0.009413026272885882</v>
       </c>
       <c r="W94">
-        <v>0.2380437175907459</v>
+        <v>0.2380195915951465</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9016,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.03806136710340802</v>
+        <v>-0.03765210509154349</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9024,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3078128409987367</v>
+        <v>0.3097128409987367</v>
       </c>
       <c r="C95">
-        <v>-7.587666535337052</v>
+        <v>-7.732505312692306</v>
       </c>
       <c r="D95">
-        <v>3.464033464662948</v>
+        <v>3.439094687307696</v>
       </c>
       <c r="E95">
-        <v>4.520700000000001</v>
+        <v>4.640600000000002</v>
       </c>
       <c r="F95">
-        <v>11.1507</v>
+        <v>11.2706</v>
       </c>
       <c r="G95">
         <v>0.099</v>
@@ -9060,37 +9071,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M95">
-        <v>2.62933506</v>
+        <v>2.657607480000001</v>
       </c>
       <c r="N95">
-        <v>-2.72833506</v>
+        <v>-2.75660748</v>
       </c>
       <c r="O95">
-        <v>-0.682083765</v>
+        <v>-0.6891518700000001</v>
       </c>
       <c r="P95">
-        <v>-2.046251295</v>
+        <v>-2.067455610000001</v>
       </c>
       <c r="Q95">
-        <v>-1.481251295</v>
+        <v>-1.502455610000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.235066011646436</v>
+        <v>1.433277013587509</v>
       </c>
       <c r="T95">
-        <v>18.39756696825518</v>
+        <v>21.46382812963105</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.009413026272885882</v>
+        <v>-0.009312887695514754</v>
       </c>
       <c r="W95">
-        <v>0.2380195915951465</v>
+        <v>0.2379959789186024</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9098,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.03765210509154349</v>
+        <v>-0.037251550782059</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9106,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3097128409987367</v>
+        <v>0.3116128409987367</v>
       </c>
       <c r="C96">
-        <v>-7.732505312692306</v>
+        <v>-7.876987570950909</v>
       </c>
       <c r="D96">
-        <v>3.439094687307696</v>
+        <v>3.414512429049091</v>
       </c>
       <c r="E96">
-        <v>4.640600000000002</v>
+        <v>4.760500000000001</v>
       </c>
       <c r="F96">
-        <v>11.2706</v>
+        <v>11.3905</v>
       </c>
       <c r="G96">
         <v>0.099</v>
@@ -9142,37 +9153,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M96">
-        <v>2.657607480000001</v>
+        <v>2.6858799</v>
       </c>
       <c r="N96">
-        <v>-2.75660748</v>
+        <v>-2.7848799</v>
       </c>
       <c r="O96">
-        <v>-0.6891518700000001</v>
+        <v>-0.696219975</v>
       </c>
       <c r="P96">
-        <v>-2.067455610000001</v>
+        <v>-2.088659925</v>
       </c>
       <c r="Q96">
-        <v>-1.502455610000001</v>
+        <v>-1.523659925</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.433277013587509</v>
+        <v>1.710772416305012</v>
       </c>
       <c r="T96">
-        <v>21.46382812963105</v>
+        <v>25.75659375555727</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.009312887695514754</v>
+        <v>-0.009214857298719865</v>
       </c>
       <c r="W96">
-        <v>0.2379959789186024</v>
+        <v>0.2379728633510381</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9180,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.037251550782059</v>
+        <v>-0.03685942919487939</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9188,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3116128409987367</v>
+        <v>0.3135128409987368</v>
       </c>
       <c r="C97">
-        <v>-7.876987570950909</v>
+        <v>-8.021120900928622</v>
       </c>
       <c r="D97">
-        <v>3.414512429049091</v>
+        <v>3.390279099071378</v>
       </c>
       <c r="E97">
-        <v>4.760500000000001</v>
+        <v>4.880400000000001</v>
       </c>
       <c r="F97">
-        <v>11.3905</v>
+        <v>11.5104</v>
       </c>
       <c r="G97">
         <v>0.099</v>
@@ -9224,37 +9235,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M97">
-        <v>2.6858799</v>
+        <v>2.71415232</v>
       </c>
       <c r="N97">
-        <v>-2.7848799</v>
+        <v>-2.81315232</v>
       </c>
       <c r="O97">
-        <v>-0.696219975</v>
+        <v>-0.70328808</v>
       </c>
       <c r="P97">
-        <v>-2.088659925</v>
+        <v>-2.10986424</v>
       </c>
       <c r="Q97">
-        <v>-1.523659925</v>
+        <v>-1.54486424</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.710772416305012</v>
+        <v>2.127015520381266</v>
       </c>
       <c r="T97">
-        <v>25.75659375555727</v>
+        <v>32.19574219444661</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.009214857298719865</v>
+        <v>-0.009118869201858198</v>
       </c>
       <c r="W97">
-        <v>0.2379728633510381</v>
+        <v>0.2379502293577982</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9262,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.03685942919487939</v>
+        <v>-0.03647547680743268</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9270,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3135128409987367</v>
+        <v>0.3154128409987367</v>
       </c>
       <c r="C98">
-        <v>-8.021120900928622</v>
+        <v>-8.164912679466966</v>
       </c>
       <c r="D98">
-        <v>3.390279099071378</v>
+        <v>3.366387320533034</v>
       </c>
       <c r="E98">
-        <v>4.880400000000001</v>
+        <v>5.0003</v>
       </c>
       <c r="F98">
-        <v>11.5104</v>
+        <v>11.6303</v>
       </c>
       <c r="G98">
         <v>0.099</v>
@@ -9306,37 +9317,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M98">
-        <v>2.71415232</v>
+        <v>2.74242474</v>
       </c>
       <c r="N98">
-        <v>-2.81315232</v>
+        <v>-2.84142474</v>
       </c>
       <c r="O98">
-        <v>-0.70328808</v>
+        <v>-0.710356185</v>
       </c>
       <c r="P98">
-        <v>-2.10986424</v>
+        <v>-2.131068555</v>
       </c>
       <c r="Q98">
-        <v>-1.54486424</v>
+        <v>-1.566068555</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.12701552038126</v>
+        <v>2.820754027175014</v>
       </c>
       <c r="T98">
-        <v>32.19574219444652</v>
+        <v>42.92765625926203</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.009118869201858198</v>
+        <v>-0.0090248602410143</v>
       </c>
       <c r="W98">
-        <v>0.2379502293577982</v>
+        <v>0.2379280620448312</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9344,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.03647547680743268</v>
+        <v>-0.03609944096405715</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9352,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3154128409987367</v>
+        <v>0.3173128409987367</v>
       </c>
       <c r="C99">
-        <v>-8.164912679466966</v>
+        <v>-8.30837007692001</v>
       </c>
       <c r="D99">
-        <v>3.366387320533034</v>
+        <v>3.342829923079989</v>
       </c>
       <c r="E99">
-        <v>5.0003</v>
+        <v>5.1202</v>
       </c>
       <c r="F99">
-        <v>11.6303</v>
+        <v>11.7502</v>
       </c>
       <c r="G99">
         <v>0.099</v>
@@ -9388,37 +9399,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M99">
-        <v>2.74242474</v>
+        <v>2.77069716</v>
       </c>
       <c r="N99">
-        <v>-2.84142474</v>
+        <v>-2.86969716</v>
       </c>
       <c r="O99">
-        <v>-0.710356185</v>
+        <v>-0.71742429</v>
       </c>
       <c r="P99">
-        <v>-2.131068555</v>
+        <v>-2.15227287</v>
       </c>
       <c r="Q99">
-        <v>-1.566068555</v>
+        <v>-1.58727287</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.820754027175014</v>
+        <v>4.20823104076252</v>
       </c>
       <c r="T99">
-        <v>42.92765625926203</v>
+        <v>64.39148438889303</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.0090248602410143</v>
+        <v>-0.008932769830391705</v>
       </c>
       <c r="W99">
-        <v>0.2379280620448312</v>
+        <v>0.2379063471260063</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9426,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.03609944096405715</v>
+        <v>-0.03573107932156683</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9434,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3173128409987367</v>
+        <v>0.3192128409987367</v>
       </c>
       <c r="C100">
-        <v>-8.30837007692001</v>
+        <v>-8.451500064328982</v>
       </c>
       <c r="D100">
-        <v>3.342829923079989</v>
+        <v>3.319599935671017</v>
       </c>
       <c r="E100">
-        <v>5.1202</v>
+        <v>5.240100000000001</v>
       </c>
       <c r="F100">
-        <v>11.7502</v>
+        <v>11.8701</v>
       </c>
       <c r="G100">
         <v>0.099</v>
@@ -9470,37 +9481,37 @@
         <v>-0.09899999999999992</v>
       </c>
       <c r="M100">
-        <v>2.77069716</v>
+        <v>2.798969580000001</v>
       </c>
       <c r="N100">
-        <v>-2.86969716</v>
+        <v>-2.89796958</v>
       </c>
       <c r="O100">
-        <v>-0.71742429</v>
+        <v>-0.7244923950000001</v>
       </c>
       <c r="P100">
-        <v>-2.15227287</v>
+        <v>-2.173477185</v>
       </c>
       <c r="Q100">
-        <v>-1.58727287</v>
+        <v>-1.608477185</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.20823104076252</v>
+        <v>8.37066208152504</v>
       </c>
       <c r="T100">
-        <v>64.39148438889303</v>
+        <v>128.7829687777861</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.008932769830391705</v>
+        <v>-0.00884253983210492</v>
       </c>
       <c r="W100">
-        <v>0.2379063471260063</v>
+        <v>0.2378850708924103</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9508,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.03573107932156683</v>
+        <v>-0.03537015932841969</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3192128409987367</v>
-      </c>
-      <c r="C101">
-        <v>-8.451500064328982</v>
-      </c>
-      <c r="D101">
-        <v>3.319599935671017</v>
-      </c>
-      <c r="E101">
-        <v>5.240100000000001</v>
-      </c>
-      <c r="F101">
-        <v>11.8701</v>
-      </c>
-      <c r="G101">
-        <v>0.099</v>
-      </c>
-      <c r="H101">
-        <v>5.36</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.466</v>
-      </c>
-      <c r="K101">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="L101">
-        <v>-0.09899999999999992</v>
-      </c>
-      <c r="M101">
-        <v>2.798969580000001</v>
-      </c>
-      <c r="N101">
-        <v>-2.89796958</v>
-      </c>
-      <c r="O101">
-        <v>-0.7244923950000001</v>
-      </c>
-      <c r="P101">
-        <v>-2.173477185</v>
-      </c>
-      <c r="Q101">
-        <v>-1.608477185</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.37066208152504</v>
-      </c>
-      <c r="T101">
-        <v>128.7829687777861</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.00884253983210492</v>
-      </c>
-      <c r="W101">
-        <v>0.2378850708924103</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.03537015932841969</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
